--- a/Prototypes/Lentil/CEData.xlsx
+++ b/Prototypes/Lentil/CEData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\Lentil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0107399-0C5A-45AA-BB8D-45A2F1B658AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99153353-16CD-465C-90B0-A78A85FDF3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A5017088-8F3F-41C2-9D3D-102B2E5948D4}"/>
+    <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" activeTab="2" xr2:uid="{A5017088-8F3F-41C2-9D3D-102B2E5948D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Roberts_etal_1988" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>TtEvn2</t>
-  </si>
-  <si>
-    <t>TtFirstFlower</t>
   </si>
   <si>
     <t>Precoz</t>
@@ -240,6 +237,9 @@
   </si>
   <si>
     <t>IWeather.MeanT</t>
+  </si>
+  <si>
+    <t>Lentil.Phenology.StartFloweringTt</t>
   </si>
 </sst>
 </file>
@@ -1234,34 +1234,34 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
         <v>51</v>
-      </c>
-      <c r="I1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" t="s">
-        <v>52</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -1270,7 +1270,7 @@
         <v>2</v>
       </c>
       <c r="M1" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -1279,10 +1279,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat0FinalT12oCFinalPp11hCVPrecoz</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>8</v>
@@ -1329,7 +1329,7 @@
         <v>Precoz</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D13" si="3">D2</f>
@@ -1379,7 +1379,7 @@
         <v>Precoz</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <f t="shared" si="3"/>
@@ -1429,7 +1429,7 @@
         <v>Precoz</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <f t="shared" si="3"/>
@@ -1479,7 +1479,7 @@
         <v>Precoz</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <f t="shared" si="3"/>
@@ -1529,7 +1529,7 @@
         <v>Precoz</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <f t="shared" si="3"/>
@@ -1579,7 +1579,7 @@
         <v>Precoz</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <f t="shared" si="3"/>
@@ -1629,7 +1629,7 @@
         <v>Precoz</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <f t="shared" si="3"/>
@@ -1679,7 +1679,7 @@
         <v>Precoz</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <f t="shared" si="3"/>
@@ -1729,7 +1729,7 @@
         <v>Precoz</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <f t="shared" si="3"/>
@@ -1779,7 +1779,7 @@
         <v>Precoz</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <f t="shared" si="3"/>
@@ -1829,7 +1829,7 @@
         <v>Precoz</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <f t="shared" si="3"/>
@@ -1879,7 +1879,7 @@
         <v>Precoz</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14">
         <v>16</v>
@@ -1926,7 +1926,7 @@
         <v>Precoz</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <f t="shared" ref="D15:D25" si="9">D14</f>
@@ -1976,7 +1976,7 @@
         <v>Precoz</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <f t="shared" si="9"/>
@@ -2026,7 +2026,7 @@
         <v>Precoz</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <f t="shared" si="9"/>
@@ -2076,7 +2076,7 @@
         <v>Precoz</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <f t="shared" si="9"/>
@@ -2126,7 +2126,7 @@
         <v>Precoz</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <f t="shared" si="9"/>
@@ -2176,7 +2176,7 @@
         <v>Precoz</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <f t="shared" si="9"/>
@@ -2226,7 +2226,7 @@
         <v>Precoz</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <f t="shared" si="9"/>
@@ -2276,7 +2276,7 @@
         <v>Precoz</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <f t="shared" si="9"/>
@@ -2326,7 +2326,7 @@
         <v>Precoz</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
@@ -2376,7 +2376,7 @@
         <v>Precoz</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
@@ -2426,7 +2426,7 @@
         <v>Precoz</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
@@ -2476,7 +2476,7 @@
         <v>Precoz</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>8</v>
@@ -2523,7 +2523,7 @@
         <v>Precoz</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <f t="shared" ref="D27:D37" si="12">D26</f>
@@ -2573,7 +2573,7 @@
         <v>Precoz</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D28">
         <f t="shared" si="12"/>
@@ -2623,7 +2623,7 @@
         <v>Precoz</v>
       </c>
       <c r="C29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <f t="shared" si="12"/>
@@ -2673,7 +2673,7 @@
         <v>Precoz</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <f t="shared" si="12"/>
@@ -2723,7 +2723,7 @@
         <v>Precoz</v>
       </c>
       <c r="C31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <f t="shared" si="12"/>
@@ -2773,7 +2773,7 @@
         <v>Precoz</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D32">
         <f t="shared" si="12"/>
@@ -2823,7 +2823,7 @@
         <v>Precoz</v>
       </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D33">
         <f t="shared" si="12"/>
@@ -2873,7 +2873,7 @@
         <v>Precoz</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D34">
         <f t="shared" si="12"/>
@@ -2923,7 +2923,7 @@
         <v>Precoz</v>
       </c>
       <c r="C35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D35">
         <f t="shared" si="12"/>
@@ -2973,7 +2973,7 @@
         <v>Precoz</v>
       </c>
       <c r="C36" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D36">
         <f t="shared" si="12"/>
@@ -3023,7 +3023,7 @@
         <v>Precoz</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D37">
         <f t="shared" si="12"/>
@@ -3073,7 +3073,7 @@
         <v>Precoz</v>
       </c>
       <c r="C38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D38">
         <v>16</v>
@@ -3120,7 +3120,7 @@
         <v>Precoz</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <f t="shared" ref="D39:D49" si="19">D38</f>
@@ -3170,7 +3170,7 @@
         <v>Precoz</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D40">
         <f t="shared" si="19"/>
@@ -3220,7 +3220,7 @@
         <v>Precoz</v>
       </c>
       <c r="C41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <f t="shared" si="19"/>
@@ -3270,7 +3270,7 @@
         <v>Precoz</v>
       </c>
       <c r="C42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D42">
         <f t="shared" si="19"/>
@@ -3320,7 +3320,7 @@
         <v>Precoz</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D43">
         <f t="shared" si="19"/>
@@ -3370,7 +3370,7 @@
         <v>Precoz</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D44">
         <f t="shared" si="19"/>
@@ -3420,7 +3420,7 @@
         <v>Precoz</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <f t="shared" si="19"/>
@@ -3470,7 +3470,7 @@
         <v>Precoz</v>
       </c>
       <c r="C46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D46">
         <f t="shared" si="19"/>
@@ -3520,7 +3520,7 @@
         <v>Precoz</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D47">
         <f t="shared" si="19"/>
@@ -3570,7 +3570,7 @@
         <v>Precoz</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D48">
         <f t="shared" si="19"/>
@@ -3620,7 +3620,7 @@
         <v>Precoz</v>
       </c>
       <c r="C49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D49">
         <f t="shared" si="19"/>
@@ -3670,7 +3670,7 @@
         <v>Precoz</v>
       </c>
       <c r="C50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D50">
         <v>8</v>
@@ -3717,7 +3717,7 @@
         <v>Precoz</v>
       </c>
       <c r="C51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D51">
         <f t="shared" ref="D51:D61" si="22">D50</f>
@@ -3766,7 +3766,7 @@
         <v>Precoz</v>
       </c>
       <c r="C52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D52">
         <f t="shared" si="22"/>
@@ -3815,7 +3815,7 @@
         <v>Precoz</v>
       </c>
       <c r="C53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D53">
         <f t="shared" si="22"/>
@@ -3864,7 +3864,7 @@
         <v>Precoz</v>
       </c>
       <c r="C54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D54">
         <f t="shared" si="22"/>
@@ -3913,7 +3913,7 @@
         <v>Precoz</v>
       </c>
       <c r="C55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D55">
         <f t="shared" si="22"/>
@@ -3962,7 +3962,7 @@
         <v>Precoz</v>
       </c>
       <c r="C56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D56">
         <f t="shared" si="22"/>
@@ -4011,7 +4011,7 @@
         <v>Precoz</v>
       </c>
       <c r="C57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D57">
         <f t="shared" si="22"/>
@@ -4060,7 +4060,7 @@
         <v>Precoz</v>
       </c>
       <c r="C58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D58">
         <f t="shared" si="22"/>
@@ -4109,7 +4109,7 @@
         <v>Precoz</v>
       </c>
       <c r="C59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D59">
         <f t="shared" si="22"/>
@@ -4158,7 +4158,7 @@
         <v>Precoz</v>
       </c>
       <c r="C60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D60">
         <f t="shared" si="22"/>
@@ -4207,7 +4207,7 @@
         <v>Precoz</v>
       </c>
       <c r="C61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61">
         <f t="shared" si="22"/>
@@ -4256,7 +4256,7 @@
         <v>Precoz</v>
       </c>
       <c r="C62" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D62">
         <v>16</v>
@@ -4303,7 +4303,7 @@
         <v>Precoz</v>
       </c>
       <c r="C63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D63">
         <f t="shared" ref="D63:D73" si="24">D62</f>
@@ -4352,7 +4352,7 @@
         <v>Precoz</v>
       </c>
       <c r="C64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D64">
         <f t="shared" si="24"/>
@@ -4401,7 +4401,7 @@
         <v>Precoz</v>
       </c>
       <c r="C65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D65">
         <f t="shared" si="24"/>
@@ -4450,7 +4450,7 @@
         <v>Precoz</v>
       </c>
       <c r="C66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D66">
         <f t="shared" si="24"/>
@@ -4499,7 +4499,7 @@
         <v>Precoz</v>
       </c>
       <c r="C67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D67">
         <f t="shared" si="24"/>
@@ -4548,7 +4548,7 @@
         <v>Precoz</v>
       </c>
       <c r="C68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D68">
         <f t="shared" si="24"/>
@@ -4597,7 +4597,7 @@
         <v>Precoz</v>
       </c>
       <c r="C69" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D69">
         <f t="shared" si="24"/>
@@ -4646,7 +4646,7 @@
         <v>Precoz</v>
       </c>
       <c r="C70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D70">
         <f t="shared" si="24"/>
@@ -4695,7 +4695,7 @@
         <v>Precoz</v>
       </c>
       <c r="C71" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D71">
         <f t="shared" si="24"/>
@@ -4744,7 +4744,7 @@
         <v>Precoz</v>
       </c>
       <c r="C72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D72">
         <f t="shared" si="24"/>
@@ -4793,7 +4793,7 @@
         <v>Precoz</v>
       </c>
       <c r="C73" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D73">
         <f t="shared" si="24"/>
@@ -4842,7 +4842,7 @@
         <v>Precoz</v>
       </c>
       <c r="C74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D74">
         <v>8</v>
@@ -4889,7 +4889,7 @@
         <v>Precoz</v>
       </c>
       <c r="C75" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D75">
         <f t="shared" ref="D75:D85" si="32">D74</f>
@@ -4938,7 +4938,7 @@
         <v>Precoz</v>
       </c>
       <c r="C76" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D76">
         <f t="shared" si="32"/>
@@ -4987,7 +4987,7 @@
         <v>Precoz</v>
       </c>
       <c r="C77" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D77">
         <f t="shared" si="32"/>
@@ -5036,7 +5036,7 @@
         <v>Precoz</v>
       </c>
       <c r="C78" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D78">
         <f t="shared" si="32"/>
@@ -5085,7 +5085,7 @@
         <v>Precoz</v>
       </c>
       <c r="C79" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D79">
         <f t="shared" si="32"/>
@@ -5134,7 +5134,7 @@
         <v>Precoz</v>
       </c>
       <c r="C80" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D80">
         <f t="shared" si="32"/>
@@ -5183,7 +5183,7 @@
         <v>Precoz</v>
       </c>
       <c r="C81" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D81">
         <f t="shared" si="32"/>
@@ -5232,7 +5232,7 @@
         <v>Precoz</v>
       </c>
       <c r="C82" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D82">
         <f t="shared" si="32"/>
@@ -5281,7 +5281,7 @@
         <v>Precoz</v>
       </c>
       <c r="C83" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D83">
         <f t="shared" si="32"/>
@@ -5330,7 +5330,7 @@
         <v>Precoz</v>
       </c>
       <c r="C84" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D84">
         <f t="shared" si="32"/>
@@ -5379,7 +5379,7 @@
         <v>Precoz</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D85">
         <f t="shared" si="32"/>
@@ -5428,7 +5428,7 @@
         <v>Precoz</v>
       </c>
       <c r="C86" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D86">
         <v>16</v>
@@ -5475,7 +5475,7 @@
         <v>Precoz</v>
       </c>
       <c r="C87" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D87">
         <f t="shared" ref="D87:D97" si="34">D86</f>
@@ -5524,7 +5524,7 @@
         <v>Precoz</v>
       </c>
       <c r="C88" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D88">
         <f t="shared" si="34"/>
@@ -5573,7 +5573,7 @@
         <v>Precoz</v>
       </c>
       <c r="C89" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D89">
         <f t="shared" si="34"/>
@@ -5622,7 +5622,7 @@
         <v>Precoz</v>
       </c>
       <c r="C90" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D90">
         <f t="shared" si="34"/>
@@ -5671,7 +5671,7 @@
         <v>Precoz</v>
       </c>
       <c r="C91" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D91">
         <f t="shared" si="34"/>
@@ -5720,7 +5720,7 @@
         <v>Precoz</v>
       </c>
       <c r="C92" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D92">
         <f t="shared" si="34"/>
@@ -5769,7 +5769,7 @@
         <v>Precoz</v>
       </c>
       <c r="C93" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D93">
         <f t="shared" si="34"/>
@@ -5818,7 +5818,7 @@
         <v>Precoz</v>
       </c>
       <c r="C94" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D94">
         <f t="shared" si="34"/>
@@ -5867,7 +5867,7 @@
         <v>Precoz</v>
       </c>
       <c r="C95" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D95">
         <f t="shared" si="34"/>
@@ -5916,7 +5916,7 @@
         <v>Precoz</v>
       </c>
       <c r="C96" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D96">
         <f t="shared" si="34"/>
@@ -5965,7 +5965,7 @@
         <v>Precoz</v>
       </c>
       <c r="C97" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D97">
         <f t="shared" si="34"/>
@@ -6010,10 +6010,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat0FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B98" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C98" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D98">
         <v>8</v>
@@ -6056,10 +6056,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat10FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B99" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C99" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D99">
         <f t="shared" ref="D99:D109" si="39">D98</f>
@@ -6105,10 +6105,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat30FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B100" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C100" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D100">
         <f t="shared" si="39"/>
@@ -6154,10 +6154,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat60FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B101" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C101" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D101">
         <f t="shared" si="39"/>
@@ -6203,10 +6203,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat0FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B102" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C102" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D102">
         <f t="shared" si="39"/>
@@ -6252,10 +6252,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat10FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B103" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C103" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D103">
         <f t="shared" si="39"/>
@@ -6301,10 +6301,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat30FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B104" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C104" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D104">
         <f t="shared" si="39"/>
@@ -6350,10 +6350,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat60FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B105" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C105" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D105">
         <f t="shared" si="39"/>
@@ -6399,10 +6399,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat0FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B106" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C106" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D106">
         <f t="shared" si="39"/>
@@ -6448,10 +6448,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat10FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B107" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C107" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D107">
         <f t="shared" si="39"/>
@@ -6497,10 +6497,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat30FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B108" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C108" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D108">
         <f t="shared" si="39"/>
@@ -6546,10 +6546,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat60FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B109" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C109" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D109">
         <f t="shared" si="39"/>
@@ -6595,10 +6595,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat0FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B110" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C110" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D110">
         <v>16</v>
@@ -6641,10 +6641,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat10FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B111" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C111" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D111">
         <f t="shared" ref="D111:D121" si="42">D110</f>
@@ -6690,10 +6690,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat30FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B112" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C112" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D112">
         <f t="shared" si="42"/>
@@ -6739,10 +6739,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat60FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B113" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C113" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D113">
         <f t="shared" si="42"/>
@@ -6788,10 +6788,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat0FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B114" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C114" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D114">
         <f t="shared" si="42"/>
@@ -6837,10 +6837,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat10FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B115" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C115" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D115">
         <f t="shared" si="42"/>
@@ -6886,10 +6886,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat30FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B116" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C116" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D116">
         <f t="shared" si="42"/>
@@ -6935,10 +6935,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat60FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B117" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C117" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D117">
         <f t="shared" si="42"/>
@@ -6984,10 +6984,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat0FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B118" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C118" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D118">
         <f t="shared" si="42"/>
@@ -7033,10 +7033,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat10FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B119" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C119" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D119">
         <f t="shared" si="42"/>
@@ -7082,10 +7082,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat30FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B120" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C120" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D120">
         <f t="shared" si="42"/>
@@ -7131,10 +7131,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat60FinalT12oCFinalPp11hCVLaird</v>
       </c>
       <c r="B121" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C121" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D121">
         <f t="shared" si="42"/>
@@ -7180,10 +7180,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat0FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B122" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C122" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D122">
         <v>8</v>
@@ -7226,10 +7226,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat10FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B123" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C123" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D123">
         <f t="shared" ref="D123:D133" si="45">D122</f>
@@ -7275,10 +7275,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat30FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B124" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C124" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D124">
         <f t="shared" si="45"/>
@@ -7324,10 +7324,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat60FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B125" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C125" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D125">
         <f t="shared" si="45"/>
@@ -7373,10 +7373,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat0FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B126" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C126" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D126">
         <f t="shared" si="45"/>
@@ -7422,10 +7422,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat10FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B127" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C127" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D127">
         <f t="shared" si="45"/>
@@ -7471,10 +7471,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat30FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B128" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C128" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D128">
         <f t="shared" si="45"/>
@@ -7520,10 +7520,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat60FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B129" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C129" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D129">
         <f t="shared" si="45"/>
@@ -7569,10 +7569,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat0FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B130" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C130" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D130">
         <f t="shared" si="45"/>
@@ -7618,10 +7618,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat10FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B131" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C131" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D131">
         <f t="shared" si="45"/>
@@ -7667,10 +7667,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat30FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B132" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C132" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D132">
         <f t="shared" si="45"/>
@@ -7716,10 +7716,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat60FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B133" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C133" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D133">
         <f t="shared" si="45"/>
@@ -7765,10 +7765,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat0FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B134" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C134" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D134">
         <v>16</v>
@@ -7811,10 +7811,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat10FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B135" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C135" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D135">
         <f t="shared" ref="D135:D145" si="53">D134</f>
@@ -7860,10 +7860,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat30FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B136" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C136" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D136">
         <f t="shared" si="53"/>
@@ -7909,10 +7909,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat60FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B137" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C137" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D137">
         <f t="shared" si="53"/>
@@ -7958,10 +7958,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat0FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B138" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C138" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D138">
         <f t="shared" si="53"/>
@@ -8007,10 +8007,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat10FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B139" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C139" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D139">
         <f t="shared" si="53"/>
@@ -8056,10 +8056,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat30FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B140" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C140" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D140">
         <f t="shared" si="53"/>
@@ -8105,10 +8105,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat60FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B141" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C141" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D141">
         <f t="shared" si="53"/>
@@ -8154,10 +8154,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat0FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B142" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C142" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D142">
         <f t="shared" si="53"/>
@@ -8203,10 +8203,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat10FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B143" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C143" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D143">
         <f t="shared" si="53"/>
@@ -8252,10 +8252,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat30FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B144" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C144" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D144">
         <f t="shared" si="53"/>
@@ -8301,10 +8301,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat60FinalT19oCFinalPp11hCVLaird</v>
       </c>
       <c r="B145" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C145" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D145">
         <f t="shared" si="53"/>
@@ -8350,10 +8350,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat0FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B146" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C146" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D146">
         <v>8</v>
@@ -8396,10 +8396,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat10FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B147" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C147" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D147">
         <f t="shared" ref="D147:D157" si="56">D146</f>
@@ -8444,10 +8444,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat30FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B148" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C148" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D148">
         <f t="shared" si="56"/>
@@ -8492,10 +8492,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat60FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B149" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C149" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D149">
         <f t="shared" si="56"/>
@@ -8540,10 +8540,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat0FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B150" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C150" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D150">
         <f t="shared" si="56"/>
@@ -8588,10 +8588,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat10FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B151" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C151" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D151">
         <f t="shared" si="56"/>
@@ -8636,10 +8636,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat30FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B152" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C152" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D152">
         <f t="shared" si="56"/>
@@ -8684,10 +8684,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat60FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B153" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C153" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D153">
         <f t="shared" si="56"/>
@@ -8732,10 +8732,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat0FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B154" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C154" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D154">
         <f t="shared" si="56"/>
@@ -8780,10 +8780,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat10FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B155" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C155" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D155">
         <f t="shared" si="56"/>
@@ -8828,10 +8828,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat30FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B156" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C156" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D156">
         <f t="shared" si="56"/>
@@ -8876,10 +8876,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat60FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B157" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C157" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D157">
         <f t="shared" si="56"/>
@@ -8924,10 +8924,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat0FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B158" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C158" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D158">
         <v>16</v>
@@ -8970,10 +8970,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat10FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B159" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C159" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D159">
         <f t="shared" ref="D159:D169" si="58">D158</f>
@@ -9018,10 +9018,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat30FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B160" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C160" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D160">
         <f t="shared" si="58"/>
@@ -9066,10 +9066,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat60FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B161" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C161" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D161">
         <f t="shared" si="58"/>
@@ -9114,10 +9114,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat0FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B162" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C162" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D162">
         <f t="shared" si="58"/>
@@ -9162,10 +9162,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat10FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B163" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C163" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D163">
         <f t="shared" si="58"/>
@@ -9210,10 +9210,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat30FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B164" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C164" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D164">
         <f t="shared" si="58"/>
@@ -9258,10 +9258,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat60FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B165" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C165" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D165">
         <f t="shared" si="58"/>
@@ -9306,10 +9306,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat0FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B166" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C166" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D166">
         <f t="shared" si="58"/>
@@ -9354,10 +9354,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat10FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B167" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C167" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D167">
         <f t="shared" si="58"/>
@@ -9402,10 +9402,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat30FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B168" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C168" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D168">
         <f t="shared" si="58"/>
@@ -9450,10 +9450,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat60FinalT12oCFinalPp16hCVLaird</v>
       </c>
       <c r="B169" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C169" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D169">
         <f t="shared" si="58"/>
@@ -9498,10 +9498,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat0FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B170" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C170" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D170">
         <v>8</v>
@@ -9544,10 +9544,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat10FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B171" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C171" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D171">
         <f t="shared" ref="D171:D181" si="63">D170</f>
@@ -9592,10 +9592,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat30FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B172" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C172" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D172">
         <f t="shared" si="63"/>
@@ -9640,10 +9640,10 @@
         <v>Roberts1988InitT1oCInitPp8hDurat60FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B173" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C173" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D173">
         <f t="shared" si="63"/>
@@ -9688,10 +9688,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat0FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B174" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C174" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D174">
         <f t="shared" si="63"/>
@@ -9736,10 +9736,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat10FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B175" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C175" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D175">
         <f t="shared" si="63"/>
@@ -9784,10 +9784,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat30FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B176" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C176" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D176">
         <f t="shared" si="63"/>
@@ -9832,10 +9832,10 @@
         <v>Roberts1988InitT5oCInitPp8hDurat60FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B177" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C177" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D177">
         <f t="shared" si="63"/>
@@ -9880,10 +9880,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat0FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B178" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C178" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D178">
         <f t="shared" si="63"/>
@@ -9928,10 +9928,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat10FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B179" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C179" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D179">
         <f t="shared" si="63"/>
@@ -9976,10 +9976,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat30FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B180" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C180" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D180">
         <f t="shared" si="63"/>
@@ -10024,10 +10024,10 @@
         <v>Roberts1988InitT9oCInitPp8hDurat60FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B181" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C181" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D181">
         <f t="shared" si="63"/>
@@ -10072,10 +10072,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat0FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B182" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C182" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D182">
         <v>16</v>
@@ -10118,10 +10118,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat10FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B183" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C183" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D183">
         <f t="shared" ref="D183:D193" si="65">D182</f>
@@ -10166,10 +10166,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat30FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B184" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C184" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D184">
         <f t="shared" si="65"/>
@@ -10214,10 +10214,10 @@
         <v>Roberts1988InitT1oCInitPp16hDurat60FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B185" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C185" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D185">
         <f t="shared" si="65"/>
@@ -10262,10 +10262,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat0FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B186" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C186" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D186">
         <f t="shared" si="65"/>
@@ -10310,10 +10310,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat10FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B187" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C187" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D187">
         <f t="shared" si="65"/>
@@ -10358,10 +10358,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat30FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B188" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C188" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D188">
         <f t="shared" si="65"/>
@@ -10406,10 +10406,10 @@
         <v>Roberts1988InitT5oCInitPp16hDurat60FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B189" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C189" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D189">
         <f t="shared" si="65"/>
@@ -10454,10 +10454,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat0FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B190" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C190" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D190">
         <f t="shared" si="65"/>
@@ -10502,10 +10502,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat10FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B191" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C191" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D191">
         <f t="shared" si="65"/>
@@ -10550,10 +10550,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat30FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B192" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C192" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D192">
         <f t="shared" si="65"/>
@@ -10598,10 +10598,10 @@
         <v>Roberts1988InitT9oCInitPp16hDurat60FinalT19oCFinalPp16hCVLaird</v>
       </c>
       <c r="B193" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C193" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D193">
         <f t="shared" si="65"/>
@@ -10656,43 +10656,43 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="L1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>51</v>
-      </c>
-      <c r="L1" t="s">
-        <v>63</v>
-      </c>
-      <c r="M1" t="s">
-        <v>52</v>
       </c>
       <c r="N1" t="s">
         <v>1</v>
@@ -10701,7 +10701,7 @@
         <v>2</v>
       </c>
       <c r="P1" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -10710,10 +10710,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp10hCvPrecoz</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -10767,10 +10767,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp10hCvPrecoz</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -10824,10 +10824,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp10hCvPrecoz</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -10881,10 +10881,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp10hCvPrecoz</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp13hCvPrecoz</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -10995,10 +10995,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp13hCvPrecoz</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -11052,10 +11052,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp13hCvPrecoz</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -11109,10 +11109,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp13hCvPrecoz</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -11166,10 +11166,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp16hCvPrecoz</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -11223,10 +11223,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp16hCvPrecoz</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -11280,10 +11280,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp16hCvPrecoz</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -11337,10 +11337,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp16hCvPrecoz</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -11394,10 +11394,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp10hCvPrecoz</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -11451,10 +11451,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp10hCvPrecoz</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -11509,10 +11509,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp10hCvPrecoz</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -11567,10 +11567,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp10hCvPrecoz</v>
       </c>
       <c r="B17" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -11625,10 +11625,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp13hCvPrecoz</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -11683,10 +11683,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp13hCvPrecoz</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -11741,10 +11741,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp13hCvPrecoz</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -11799,10 +11799,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp13hCvPrecoz</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -11857,10 +11857,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp16hCvPrecoz</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -11915,10 +11915,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp16hCvPrecoz</v>
       </c>
       <c r="B23" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -11973,10 +11973,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp16hCvPrecoz</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -12031,10 +12031,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp16hCvPrecoz</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -12089,10 +12089,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp10hCvEthiopia</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -12146,10 +12146,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp10hCvEthiopia</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -12203,10 +12203,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp10hCvEthiopia</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -12260,10 +12260,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp10hCvEthiopia</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -12317,10 +12317,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp13hCvEthiopia</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -12374,10 +12374,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp13hCvEthiopia</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -12431,10 +12431,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp13hCvEthiopia</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -12488,10 +12488,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp13hCvEthiopia</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -12545,10 +12545,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp16hCvEthiopia</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp16hCvEthiopia</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -12659,10 +12659,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp16hCvEthiopia</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -12716,10 +12716,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp16hCvEthiopia</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -12773,10 +12773,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp10hCvEthiopia</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
@@ -12830,10 +12830,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp10hCvEthiopia</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -12888,10 +12888,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp10hCvEthiopia</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -12946,10 +12946,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp10hCvEthiopia</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -13004,10 +13004,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp13hCvEthiopia</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp13hCvEthiopia</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -13120,10 +13120,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp13hCvEthiopia</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -13178,10 +13178,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp13hCvEthiopia</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -13236,10 +13236,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp16hCvEthiopia</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -13294,10 +13294,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp16hCvEthiopia</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -13352,10 +13352,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp16hCvEthiopia</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -13410,10 +13410,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp16hCvEthiopia</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -13468,10 +13468,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp10hCvLaird</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
@@ -13525,10 +13525,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp10hCvLaird</v>
       </c>
       <c r="B51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C51" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -13582,10 +13582,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp10hCvLaird</v>
       </c>
       <c r="B52" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -13639,10 +13639,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp10hCvLaird</v>
       </c>
       <c r="B53" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -13696,10 +13696,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp13hCvLaird</v>
       </c>
       <c r="B54" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -13753,10 +13753,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp13hCvLaird</v>
       </c>
       <c r="B55" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -13810,10 +13810,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp13hCvLaird</v>
       </c>
       <c r="B56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -13867,10 +13867,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp13hCvLaird</v>
       </c>
       <c r="B57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -13924,10 +13924,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp16hCvLaird</v>
       </c>
       <c r="B58" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -13962,10 +13962,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp16hCvLaird</v>
       </c>
       <c r="B59" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -14000,10 +14000,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp16hCvLaird</v>
       </c>
       <c r="B60" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -14038,10 +14038,10 @@
         <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp16hCvLaird</v>
       </c>
       <c r="B61" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -14076,10 +14076,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp10hCvLaird</v>
       </c>
       <c r="B62" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
@@ -14114,10 +14114,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp10hCvLaird</v>
       </c>
       <c r="B63" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C63" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -14153,10 +14153,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp10hCvLaird</v>
       </c>
       <c r="B64" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -14192,10 +14192,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp10hCvLaird</v>
       </c>
       <c r="B65" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -14231,10 +14231,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp13hCvLaird</v>
       </c>
       <c r="B66" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -14289,10 +14289,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp13hCvLaird</v>
       </c>
       <c r="B67" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -14328,10 +14328,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp13hCvLaird</v>
       </c>
       <c r="B68" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -14386,10 +14386,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp13hCvLaird</v>
       </c>
       <c r="B69" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -14444,10 +14444,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp16hCvLaird</v>
       </c>
       <c r="B70" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C70" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -14502,10 +14502,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp16hCvLaird</v>
       </c>
       <c r="B71" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C71" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -14560,10 +14560,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp16hCvLaird</v>
       </c>
       <c r="B72" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C72" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -14618,10 +14618,10 @@
         <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp16hCvLaird</v>
       </c>
       <c r="B73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C73" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -14666,34 +14666,34 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" t="s">
         <v>51</v>
-      </c>
-      <c r="I1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" t="s">
-        <v>52</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -14702,22 +14702,22 @@
         <v>2</v>
       </c>
       <c r="M1" t="s">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="N1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q1" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" t="s">
-        <v>49</v>
-      </c>
       <c r="R1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -14726,10 +14726,10 @@
         <v>Roberts1986Pp10to16hDurat45CvSyrian</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -14765,7 +14765,7 @@
         <v>1478.5321100917445</v>
       </c>
       <c r="N2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O2">
         <f>F2*MIN(H2,I2)</f>
@@ -14790,10 +14790,10 @@
         <v>Roberts1986Pp10to16hDurat41CvSyrian</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
       </c>
       <c r="D3" s="1">
         <v>10</v>
@@ -14829,7 +14829,7 @@
         <v>1428.623853211009</v>
       </c>
       <c r="N3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O66" si="4">F3*MIN(H3,I3)</f>
@@ -14854,10 +14854,10 @@
         <v>Roberts1986Pp10to16hDurat37CvSyrian</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
       </c>
       <c r="D4" s="1">
         <v>10</v>
@@ -14893,7 +14893,7 @@
         <v>1335.045871559631</v>
       </c>
       <c r="N4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O4">
         <f t="shared" si="4"/>
@@ -14918,10 +14918,10 @@
         <v>Roberts1986Pp10to16hDurat33CvSyrian</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
       </c>
       <c r="D5" s="1">
         <v>10</v>
@@ -14957,7 +14957,7 @@
         <v>1241.4678899082564</v>
       </c>
       <c r="N5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O5">
         <f t="shared" si="4"/>
@@ -14982,10 +14982,10 @@
         <v>Roberts1986Pp10to16hDurat29CvSyrian</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
       </c>
       <c r="D6" s="1">
         <v>10</v>
@@ -15021,7 +15021,7 @@
         <v>1122.9357798165133</v>
       </c>
       <c r="N6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O6">
         <f t="shared" si="4"/>
@@ -15046,10 +15046,10 @@
         <v>Roberts1986Pp10to16hDurat25CvSyrian</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
         <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
       </c>
       <c r="D7" s="1">
         <v>10</v>
@@ -15085,7 +15085,7 @@
         <v>1066.7889908256873</v>
       </c>
       <c r="N7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O7">
         <f t="shared" si="4"/>
@@ -15110,10 +15110,10 @@
         <v>Roberts1986Pp10to16hDurat21CvSyrian</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s">
         <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
       </c>
       <c r="D8" s="1">
         <v>10</v>
@@ -15149,7 +15149,7 @@
         <v>979.44954128440099</v>
       </c>
       <c r="N8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O8">
         <f t="shared" si="4"/>
@@ -15174,10 +15174,10 @@
         <v>Roberts1986Pp10to16hDurat17CvSyrian</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
         <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
       </c>
       <c r="D9" s="1">
         <v>10</v>
@@ -15213,7 +15213,7 @@
         <v>904.58715596330046</v>
       </c>
       <c r="N9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O9">
         <f t="shared" si="4"/>
@@ -15238,10 +15238,10 @@
         <v>Roberts1986Pp10to16hDurat13CvSyrian</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
         <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
       </c>
       <c r="D10" s="1">
         <v>10</v>
@@ -15277,7 +15277,7 @@
         <v>792.29357798164858</v>
       </c>
       <c r="N10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O10">
         <f t="shared" si="4"/>
@@ -15302,10 +15302,10 @@
         <v>Roberts1986Pp10to16hDurat9CvSyrian</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
         <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
@@ -15341,7 +15341,7 @@
         <v>786.05504587155724</v>
       </c>
       <c r="N11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O11">
         <f t="shared" si="4"/>
@@ -15366,10 +15366,10 @@
         <v>Roberts1986Pp10to16hDurat0CvSyrian</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
         <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
       </c>
       <c r="D12" s="1">
         <v>10</v>
@@ -15405,7 +15405,7 @@
         <v>748.62385321100896</v>
       </c>
       <c r="N12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O12">
         <f t="shared" si="4"/>
@@ -15430,10 +15430,10 @@
         <v>Roberts1986Pp16to10hDurat45CvSyrian</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
         <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
       </c>
       <c r="D13" s="1">
         <v>16</v>
@@ -15469,7 +15469,7 @@
         <v>723.66972477063985</v>
       </c>
       <c r="N13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O13">
         <f t="shared" si="4"/>
@@ -15494,10 +15494,10 @@
         <v>Roberts1986Pp16to10hDurat41CvSyrian</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
         <v>11</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
       </c>
       <c r="D14" s="1">
         <v>16</v>
@@ -15533,7 +15533,7 @@
         <v>748.62385321100896</v>
       </c>
       <c r="N14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O14">
         <f t="shared" si="4"/>
@@ -15558,10 +15558,10 @@
         <v>Roberts1986Pp16to10hDurat37CvSyrian</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
         <v>11</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
       </c>
       <c r="D15" s="1">
         <v>16</v>
@@ -15597,7 +15597,7 @@
         <v>742.38532110091739</v>
       </c>
       <c r="N15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O15">
         <f t="shared" si="4"/>
@@ -15622,10 +15622,10 @@
         <v>Roberts1986Pp16to10hDurat33CvSyrian</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
         <v>11</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
       </c>
       <c r="D16" s="1">
         <v>16</v>
@@ -15661,7 +15661,7 @@
         <v>748.62385321100896</v>
       </c>
       <c r="N16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O16">
         <f t="shared" si="4"/>
@@ -15686,10 +15686,10 @@
         <v>Roberts1986Pp16to10hDurat29CvSyrian</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
         <v>11</v>
-      </c>
-      <c r="C17" t="s">
-        <v>12</v>
       </c>
       <c r="D17" s="1">
         <v>16</v>
@@ -15725,7 +15725,7 @@
         <v>765</v>
       </c>
       <c r="N17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O17">
         <f t="shared" si="4"/>
@@ -15750,10 +15750,10 @@
         <v>Roberts1986Pp16to10hDurat25CvSyrian</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" t="s">
         <v>11</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
       </c>
       <c r="D18" s="1">
         <v>16</v>
@@ -15789,7 +15789,7 @@
         <v>754.86238532110019</v>
       </c>
       <c r="N18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O18">
         <f t="shared" si="4"/>
@@ -15814,10 +15814,10 @@
         <v>Roberts1986Pp16to10hDurat21CvSyrian</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
         <v>11</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
       </c>
       <c r="D19" s="1">
         <v>16</v>
@@ -15853,7 +15853,7 @@
         <v>2046.2385321100915</v>
       </c>
       <c r="N19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O19">
         <f t="shared" si="4"/>
@@ -15878,10 +15878,10 @@
         <v>Roberts1986Pp16to10hDurat17CvSyrian</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
         <v>11</v>
-      </c>
-      <c r="C20" t="s">
-        <v>12</v>
       </c>
       <c r="D20" s="1">
         <v>16</v>
@@ -15917,7 +15917,7 @@
         <v>2832.2935779816517</v>
       </c>
       <c r="N20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O20">
         <f t="shared" si="4"/>
@@ -15942,10 +15942,10 @@
         <v>Roberts1986Pp16to10hDurat13CvSyrian</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" t="s">
         <v>11</v>
-      </c>
-      <c r="C21" t="s">
-        <v>12</v>
       </c>
       <c r="D21" s="1">
         <v>16</v>
@@ -15981,7 +15981,7 @@
         <v>2944.5871559633006</v>
       </c>
       <c r="N21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O21">
         <f t="shared" si="4"/>
@@ -16006,10 +16006,10 @@
         <v>Roberts1986Pp16to10hDurat9CvSyrian</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
         <v>11</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
       </c>
       <c r="D22" s="1">
         <v>16</v>
@@ -16045,7 +16045,7 @@
         <v>2189.7247706422004</v>
       </c>
       <c r="N22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O22">
         <f t="shared" si="4"/>
@@ -16070,10 +16070,10 @@
         <v>Roberts1986Pp16to10hDurat0CvSyrian</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
         <v>11</v>
-      </c>
-      <c r="C23" t="s">
-        <v>12</v>
       </c>
       <c r="D23" s="1">
         <v>16</v>
@@ -16109,7 +16109,7 @@
         <v>2713.7614678899085</v>
       </c>
       <c r="N23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O23">
         <f t="shared" si="4"/>
@@ -16134,10 +16134,10 @@
         <v>Roberts1986Pp10to16hDurat45CvLaird</v>
       </c>
       <c r="B24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="1">
         <v>10</v>
@@ -16173,7 +16173,7 @@
         <v>1448.4333101074726</v>
       </c>
       <c r="N24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O24">
         <f t="shared" si="4"/>
@@ -16198,10 +16198,10 @@
         <v>Roberts1986Pp10to16hDurat41CvLaird</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="1">
         <v>10</v>
@@ -16237,7 +16237,7 @@
         <v>1293.0549397183331</v>
       </c>
       <c r="N25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O25">
         <f t="shared" si="4"/>
@@ -16262,10 +16262,10 @@
         <v>Roberts1986Pp10to16hDurat37CvLaird</v>
       </c>
       <c r="B26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="1">
         <v>10</v>
@@ -16301,7 +16301,7 @@
         <v>1289.8872490023416</v>
       </c>
       <c r="N26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O26">
         <f t="shared" si="4"/>
@@ -16326,10 +16326,10 @@
         <v>Roberts1986Pp10to16hDurat33CvLaird</v>
       </c>
       <c r="B27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="1">
         <v>10</v>
@@ -16365,7 +16365,7 @@
         <v>1226.8834061780783</v>
       </c>
       <c r="N27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O27">
         <f t="shared" si="4"/>
@@ -16390,10 +16390,10 @@
         <v>Roberts1986Pp10to16hDurat29CvLaird</v>
       </c>
       <c r="B28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="1">
         <v>10</v>
@@ -16429,7 +16429,7 @@
         <v>1246.8407550516242</v>
       </c>
       <c r="N28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O28">
         <f t="shared" si="4"/>
@@ -16454,10 +16454,10 @@
         <v>Roberts1986Pp10to16hDurat25CvLaird</v>
       </c>
       <c r="B29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="1">
         <v>10</v>
@@ -16493,7 +16493,7 @@
         <v>1234.4481746584738</v>
       </c>
       <c r="N29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O29">
         <f t="shared" si="4"/>
@@ -16518,10 +16518,10 @@
         <v>Roberts1986Pp10to16hDurat21CvLaird</v>
       </c>
       <c r="B30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="1">
         <v>10</v>
@@ -16557,7 +16557,7 @@
         <v>1175.805515086251</v>
       </c>
       <c r="N30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O30">
         <f t="shared" si="4"/>
@@ -16582,10 +16582,10 @@
         <v>Roberts1986Pp10to16hDurat17CvLaird</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="1">
         <v>10</v>
@@ -16621,7 +16621,7 @@
         <v>1186.4751588860031</v>
       </c>
       <c r="N31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O31">
         <f t="shared" si="4"/>
@@ -16646,10 +16646,10 @@
         <v>Roberts1986Pp10to16hDurat13CvLaird</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="1">
         <v>10</v>
@@ -16685,7 +16685,7 @@
         <v>1151.0831696965845</v>
       </c>
       <c r="N32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O32">
         <f t="shared" si="4"/>
@@ -16710,10 +16710,10 @@
         <v>Roberts1986Pp10to16hDurat9CvLaird</v>
       </c>
       <c r="B33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="1">
         <v>10</v>
@@ -16749,7 +16749,7 @@
         <v>1170.9148877768614</v>
       </c>
       <c r="N33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O33">
         <f t="shared" si="4"/>
@@ -16774,10 +16774,10 @@
         <v>Roberts1986Pp10to16hDurat0CvLaird</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="1">
         <v>10</v>
@@ -16813,7 +16813,7 @@
         <v>1144.7477882646058</v>
       </c>
       <c r="N34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O34">
         <f t="shared" si="4"/>
@@ -16838,10 +16838,10 @@
         <v>Roberts1986Pp16to10hDurat45CvLaird</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="1">
         <v>16</v>
@@ -16877,7 +16877,7 @@
         <v>1187.7045459344179</v>
       </c>
       <c r="N35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O35">
         <f t="shared" si="4"/>
@@ -16902,10 +16902,10 @@
         <v>Roberts1986Pp16to10hDurat41CvLaird</v>
       </c>
       <c r="B36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="1">
         <v>16</v>
@@ -16941,7 +16941,7 @@
         <v>1161.4746310255266</v>
       </c>
       <c r="N36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O36">
         <f t="shared" si="4"/>
@@ -16966,10 +16966,10 @@
         <v>Roberts1986Pp16to10hDurat37CvLaird</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="1">
         <v>16</v>
@@ -17005,7 +17005,7 @@
         <v>1453.5034099786728</v>
       </c>
       <c r="N37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O37">
         <f t="shared" si="4"/>
@@ -17030,10 +17030,10 @@
         <v>Roberts1986Pp16to10hDurat33CvLaird</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="1">
         <v>16</v>
@@ -17069,7 +17069,7 @@
         <v>1676.4711471463841</v>
       </c>
       <c r="N38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O38">
         <f t="shared" si="4"/>
@@ -17094,10 +17094,10 @@
         <v>Roberts1986Pp16to10hDurat29CvLaird</v>
       </c>
       <c r="B39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" s="1">
         <v>16</v>
@@ -17133,7 +17133,7 @@
         <v>1354.9819471717219</v>
       </c>
       <c r="N39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O39">
         <f t="shared" si="4"/>
@@ -17158,10 +17158,10 @@
         <v>Roberts1986Pp16to10hDurat25CvLaird</v>
       </c>
       <c r="B40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="1">
         <v>16</v>
@@ -17197,7 +17197,7 @@
         <v>1997.5565338569704</v>
       </c>
       <c r="N40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O40">
         <f t="shared" si="4"/>
@@ -17222,10 +17222,10 @@
         <v>Roberts1986Pp16to10hDurat21CvLaird</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41" s="1">
         <v>16</v>
@@ -17261,7 +17261,7 @@
         <v>1929.8146154008555</v>
       </c>
       <c r="N41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O41">
         <f t="shared" si="4"/>
@@ -17286,10 +17286,10 @@
         <v>Roberts1986Pp16to10hDurat17CvLaird</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42" s="1">
         <v>16</v>
@@ -17325,7 +17325,7 @@
         <v>2143.4946474947692</v>
       </c>
       <c r="N42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O42">
         <f t="shared" si="4"/>
@@ -17350,10 +17350,10 @@
         <v>Roberts1986Pp16to10hDurat13CvLaird</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43" s="1">
         <v>16</v>
@@ -17389,7 +17389,7 @@
         <v>2463.3865416692888</v>
       </c>
       <c r="N43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O43">
         <f t="shared" si="4"/>
@@ -17414,10 +17414,10 @@
         <v>Roberts1986Pp16to10hDurat9CvLaird</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D44" s="1">
         <v>16</v>
@@ -17453,7 +17453,7 @@
         <v>2229.4709782310288</v>
       </c>
       <c r="N44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O44">
         <f t="shared" si="4"/>
@@ -17478,10 +17478,10 @@
         <v>Roberts1986Pp16to10hDurat0CvLaird</v>
       </c>
       <c r="B45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D45" s="1">
         <v>16</v>
@@ -17517,7 +17517,7 @@
         <v>1861.8573298705689</v>
       </c>
       <c r="N45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O45">
         <f t="shared" si="4"/>
@@ -17542,10 +17542,10 @@
         <v>Roberts1986Pp10to16hDurat45CvPrecoz</v>
       </c>
       <c r="B46" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D46" s="1">
         <v>10</v>
@@ -17581,7 +17581,7 @@
         <v>1120.5163142213498</v>
       </c>
       <c r="N46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O46">
         <f t="shared" si="4"/>
@@ -17606,10 +17606,10 @@
         <v>Roberts1986Pp10to16hDurat41CvPrecoz</v>
       </c>
       <c r="B47" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D47" s="1">
         <v>10</v>
@@ -17645,7 +17645,7 @@
         <v>1087.7170990480333</v>
       </c>
       <c r="N47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O47">
         <f t="shared" si="4"/>
@@ -17670,10 +17670,10 @@
         <v>Roberts1986Pp10to16hDurat37CvPrecoz</v>
       </c>
       <c r="B48" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D48" s="1">
         <v>10</v>
@@ -17709,7 +17709,7 @@
         <v>1140.7764697333041</v>
       </c>
       <c r="N48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O48">
         <f t="shared" si="4"/>
@@ -17734,10 +17734,10 @@
         <v>Roberts1986Pp10to16hDurat33CvPrecoz</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C49" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D49" s="1">
         <v>10</v>
@@ -17773,7 +17773,7 @@
         <v>1095.0984666811999</v>
       </c>
       <c r="N49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O49">
         <f t="shared" si="4"/>
@@ -17798,10 +17798,10 @@
         <v>Roberts1986Pp10to16hDurat29CvPrecoz</v>
       </c>
       <c r="B50" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D50" s="1">
         <v>10</v>
@@ -17837,7 +17837,7 @@
         <v>1058.0680909817593</v>
       </c>
       <c r="N50" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O50">
         <f t="shared" si="4"/>
@@ -17862,10 +17862,10 @@
         <v>Roberts1986Pp10to16hDurat25CvPrecoz</v>
       </c>
       <c r="B51" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D51" s="1">
         <v>10</v>
@@ -17901,7 +17901,7 @@
         <v>986.6942809388845</v>
       </c>
       <c r="N51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O51">
         <f t="shared" si="4"/>
@@ -17926,10 +17926,10 @@
         <v>Roberts1986Pp10to16hDurat21CvPrecoz</v>
       </c>
       <c r="B52" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D52" s="1">
         <v>10</v>
@@ -17965,7 +17965,7 @@
         <v>962.48092435142655</v>
       </c>
       <c r="N52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O52">
         <f t="shared" si="4"/>
@@ -17990,10 +17990,10 @@
         <v>Roberts1986Pp10to16hDurat17CvPrecoz</v>
       </c>
       <c r="B53" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D53" s="1">
         <v>10</v>
@@ -18029,7 +18029,7 @@
         <v>912.32468570598076</v>
       </c>
       <c r="N53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O53">
         <f t="shared" si="4"/>
@@ -18054,10 +18054,10 @@
         <v>Roberts1986Pp10to16hDurat13CvPrecoz</v>
       </c>
       <c r="B54" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D54" s="1">
         <v>10</v>
@@ -18093,7 +18093,7 @@
         <v>871.00138071361073</v>
       </c>
       <c r="N54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O54">
         <f t="shared" si="4"/>
@@ -18118,10 +18118,10 @@
         <v>Roberts1986Pp10to16hDurat9CvPrecoz</v>
       </c>
       <c r="B55" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D55" s="1">
         <v>10</v>
@@ -18157,7 +18157,7 @@
         <v>838.38747184070905</v>
       </c>
       <c r="N55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O55">
         <f t="shared" si="4"/>
@@ -18182,10 +18182,10 @@
         <v>Roberts1986Pp10to16hDurat0CvPrecoz</v>
       </c>
       <c r="B56" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D56" s="1">
         <v>10</v>
@@ -18221,7 +18221,7 @@
         <v>839.86992224402172</v>
       </c>
       <c r="N56" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O56">
         <f t="shared" si="4"/>
@@ -18246,10 +18246,10 @@
         <v>Roberts1986Pp16to10hDurat45CvPrecoz</v>
       </c>
       <c r="B57" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D57" s="1">
         <v>16</v>
@@ -18285,7 +18285,7 @@
         <v>858.46232105224874</v>
       </c>
       <c r="N57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O57">
         <f t="shared" si="4"/>
@@ -18310,10 +18310,10 @@
         <v>Roberts1986Pp16to10hDurat41CvPrecoz</v>
       </c>
       <c r="B58" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D58" s="1">
         <v>16</v>
@@ -18349,7 +18349,7 @@
         <v>851.54421917011757</v>
       </c>
       <c r="N58" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O58">
         <f t="shared" si="4"/>
@@ -18374,10 +18374,10 @@
         <v>Roberts1986Pp16to10hDurat37CvPrecoz</v>
       </c>
       <c r="B59" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D59" s="1">
         <v>16</v>
@@ -18413,7 +18413,7 @@
         <v>861.6742969260938</v>
       </c>
       <c r="N59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O59">
         <f t="shared" si="4"/>
@@ -18438,10 +18438,10 @@
         <v>Roberts1986Pp16to10hDurat33CvPrecoz</v>
       </c>
       <c r="B60" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D60" s="1">
         <v>16</v>
@@ -18477,7 +18477,7 @@
         <v>824.58215245985025</v>
       </c>
       <c r="N60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O60">
         <f t="shared" si="4"/>
@@ -18502,10 +18502,10 @@
         <v>Roberts1986Pp16to10hDurat29CvPrecoz</v>
       </c>
       <c r="B61" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61" s="1">
         <v>16</v>
@@ -18541,7 +18541,7 @@
         <v>890.52031102390652</v>
       </c>
       <c r="N61" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O61">
         <f t="shared" si="4"/>
@@ -18566,10 +18566,10 @@
         <v>Roberts1986Pp16to10hDurat25CvPrecoz</v>
       </c>
       <c r="B62" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C62" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D62" s="1">
         <v>16</v>
@@ -18605,7 +18605,7 @@
         <v>952.28907782864565</v>
       </c>
       <c r="N62" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O62">
         <f t="shared" si="4"/>
@@ -18630,10 +18630,10 @@
         <v>Roberts1986Pp16to10hDurat21CvPrecoz</v>
       </c>
       <c r="B63" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D63" s="1">
         <v>16</v>
@@ -18669,7 +18669,7 @@
         <v>966.58854734394129</v>
       </c>
       <c r="N63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O63">
         <f t="shared" si="4"/>
@@ -18694,10 +18694,10 @@
         <v>Roberts1986Pp16to10hDurat17CvPrecoz</v>
       </c>
       <c r="B64" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C64" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D64" s="1">
         <v>16</v>
@@ -18733,7 +18733,7 @@
         <v>1152.7904948768257</v>
       </c>
       <c r="N64" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O64">
         <f t="shared" si="4"/>
@@ -18758,10 +18758,10 @@
         <v>Roberts1986Pp16to10hDurat13CvPrecoz</v>
       </c>
       <c r="B65" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D65" s="1">
         <v>16</v>
@@ -18797,7 +18797,7 @@
         <v>1132.931836349102</v>
       </c>
       <c r="N65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O65">
         <f t="shared" si="4"/>
@@ -18822,10 +18822,10 @@
         <v>Roberts1986Pp16to10hDurat9CvPrecoz</v>
       </c>
       <c r="B66" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C66" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D66" s="1">
         <v>16</v>
@@ -18861,7 +18861,7 @@
         <v>1146.9842307971803</v>
       </c>
       <c r="N66" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O66">
         <f t="shared" si="4"/>
@@ -18886,10 +18886,10 @@
         <v>Roberts1986Pp16to10hDurat0CvPrecoz</v>
       </c>
       <c r="B67" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C67" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D67" s="1">
         <v>16</v>
@@ -18925,7 +18925,7 @@
         <v>1161.777850446915</v>
       </c>
       <c r="N67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O67">
         <f t="shared" ref="O67" si="12">F67*MIN(H67,I67)</f>
@@ -18950,10 +18950,10 @@
         <v>Roberts1986Pp8to16hDurat45CvPrecoz</v>
       </c>
       <c r="B68" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C68" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D68" s="1">
         <v>8</v>
@@ -18986,7 +18986,7 @@
         <v>1630.1396322520613</v>
       </c>
       <c r="N68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -18995,10 +18995,10 @@
         <v>Roberts1986Pp8to16hDurat41CvPrecoz</v>
       </c>
       <c r="B69" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C69" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D69" s="1">
         <v>8</v>
@@ -19031,7 +19031,7 @@
         <v>1390.0948717140002</v>
       </c>
       <c r="N69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -19040,10 +19040,10 @@
         <v>Roberts1986Pp8to16hDurat37CvPrecoz</v>
       </c>
       <c r="B70" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C70" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D70" s="1">
         <v>8</v>
@@ -19076,7 +19076,7 @@
         <v>1365.8459653383368</v>
       </c>
       <c r="N70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
@@ -19085,10 +19085,10 @@
         <v>Roberts1986Pp8to16hDurat33CvPrecoz</v>
       </c>
       <c r="B71" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C71" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D71" s="1">
         <v>8</v>
@@ -19121,7 +19121,7 @@
         <v>1332.9574661347037</v>
       </c>
       <c r="N71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -19130,10 +19130,10 @@
         <v>Roberts1986Pp8to16hDurat29CvPrecoz</v>
       </c>
       <c r="B72" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C72" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D72" s="1">
         <v>8</v>
@@ -19166,7 +19166,7 @@
         <v>1235.3245533250265</v>
       </c>
       <c r="N72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
@@ -19175,10 +19175,10 @@
         <v>Roberts1986Pp8to16hDurat25CvPrecoz</v>
       </c>
       <c r="B73" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C73" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D73" s="1">
         <v>8</v>
@@ -19211,7 +19211,7 @@
         <v>1258.5570387775358</v>
       </c>
       <c r="N73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
@@ -19220,10 +19220,10 @@
         <v>Roberts1986Pp8to16hDurat21CvPrecoz</v>
       </c>
       <c r="B74" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D74" s="1">
         <v>8</v>
@@ -19256,7 +19256,7 @@
         <v>1165.2237175342582</v>
       </c>
       <c r="N74" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -19265,10 +19265,10 @@
         <v>Roberts1986Pp8to16hDurat17CvPrecoz</v>
       </c>
       <c r="B75" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D75" s="1">
         <v>8</v>
@@ -19301,7 +19301,7 @@
         <v>1115.0721965527555</v>
       </c>
       <c r="N75" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
@@ -19310,10 +19310,10 @@
         <v>Roberts1986Pp8to16hDurat13CvPrecoz</v>
       </c>
       <c r="B76" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D76" s="1">
         <v>8</v>
@@ -19346,7 +19346,7 @@
         <v>1073.5764322772916</v>
       </c>
       <c r="N76" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
@@ -19355,10 +19355,10 @@
         <v>Roberts1986Pp8to16hDurat9CvPrecoz</v>
       </c>
       <c r="B77" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D77" s="1">
         <v>8</v>
@@ -19391,7 +19391,7 @@
         <v>1044.9794427010213</v>
       </c>
       <c r="N77" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
@@ -19400,10 +19400,10 @@
         <v>Roberts1986Pp8to16hDurat0CvPrecoz</v>
       </c>
       <c r="B78" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D78" s="1">
         <v>8</v>
@@ -19436,7 +19436,7 @@
         <v>1082.1769195590789</v>
       </c>
       <c r="N78" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
@@ -19445,10 +19445,10 @@
         <v>Roberts1986Pp16to8hDurat49CvPrecoz</v>
       </c>
       <c r="B79" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D79" s="1">
         <v>16</v>
@@ -19481,7 +19481,7 @@
         <v>999.3075158090594</v>
       </c>
       <c r="N79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
@@ -19490,10 +19490,10 @@
         <v>Roberts1986Pp16to8hDurat45CvPrecoz</v>
       </c>
       <c r="B80" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D80" s="1">
         <v>16</v>
@@ -19526,7 +19526,7 @@
         <v>1024.126448835412</v>
       </c>
       <c r="N80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
@@ -19535,10 +19535,10 @@
         <v>Roberts1986Pp16to8hDurat41CvPrecoz</v>
       </c>
       <c r="B81" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D81" s="1">
         <v>16</v>
@@ -19571,7 +19571,7 @@
         <v>955.9555438159357</v>
       </c>
       <c r="N81" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
@@ -19580,10 +19580,10 @@
         <v>Roberts1986Pp16to8hDurat37CvPrecoz</v>
       </c>
       <c r="B82" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D82" s="1">
         <v>16</v>
@@ -19616,7 +19616,7 @@
         <v>976.54017788150657</v>
       </c>
       <c r="N82" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
@@ -19625,10 +19625,10 @@
         <v>Roberts1986Pp16to8hDurat33CvPrecoz</v>
       </c>
       <c r="B83" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D83" s="1">
         <v>16</v>
@@ -19661,7 +19661,7 @@
         <v>1015.8631621276385</v>
       </c>
       <c r="N83" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
@@ -19670,10 +19670,10 @@
         <v>Roberts1986Pp16to8hDurat29CvPrecoz</v>
       </c>
       <c r="B84" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D84" s="1">
         <v>16</v>
@@ -19706,7 +19706,7 @@
         <v>1036.4740526390474</v>
       </c>
       <c r="N84" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
@@ -19715,10 +19715,10 @@
         <v>Roberts1986Pp16to8hDurat25CvPrecoz</v>
       </c>
       <c r="B85" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D85" s="1">
         <v>16</v>
@@ -19751,7 +19751,7 @@
         <v>1435.6766357056113</v>
       </c>
       <c r="N85" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
@@ -19760,10 +19760,10 @@
         <v>Roberts1986Pp16to8hDurat21CvPrecoz</v>
       </c>
       <c r="B86" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D86" s="1">
         <v>16</v>
@@ -19796,7 +19796,7 @@
         <v>1493.6767050920153</v>
       </c>
       <c r="N86" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
@@ -19805,10 +19805,10 @@
         <v>Roberts1986Pp16to8hDurat17CvPrecoz</v>
       </c>
       <c r="B87" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D87" s="1">
         <v>16</v>
@@ -19841,7 +19841,7 @@
         <v>1593.7571050100125</v>
       </c>
       <c r="N87" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
@@ -19850,10 +19850,10 @@
         <v>Roberts1986Pp16to8hDurat13CvPrecoz</v>
       </c>
       <c r="B88" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D88" s="1">
         <v>16</v>
@@ -19886,7 +19886,7 @@
         <v>1684.4552016148089</v>
       </c>
       <c r="N88" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
@@ -19895,10 +19895,10 @@
         <v>Roberts1986Pp16to8hDurat9CvPrecoz</v>
       </c>
       <c r="B89" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D89" s="1">
         <v>16</v>
@@ -19931,7 +19931,7 @@
         <v>1789.1917445949557</v>
       </c>
       <c r="N89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
@@ -19940,10 +19940,10 @@
         <v>Roberts1986Pp16to8hDurat0CvPrecoz</v>
       </c>
       <c r="B90" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D90" s="1">
         <v>16</v>
@@ -19976,7 +19976,7 @@
         <v>1766.9187705990873</v>
       </c>
       <c r="N90" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
@@ -19999,24 +19999,24 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" t="s">
         <v>42</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>43</v>
-      </c>
-      <c r="D1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C2">
         <v>0.41868386608424402</v>
@@ -20031,7 +20031,7 @@
         <v>A</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3">
         <v>45.0506993834071</v>
@@ -20046,7 +20046,7 @@
         <v>A</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4">
         <v>75.787299134246894</v>
@@ -20055,18 +20055,18 @@
         <v>0.98967877249144398</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5">
         <v>0.19869742797218401</v>
@@ -20075,16 +20075,16 @@
         <v>0.94382066768643602</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
         <v>37</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>38</v>
-      </c>
-      <c r="J5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -20093,7 +20093,7 @@
         <v>b</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6">
         <v>41.462318452052401</v>
@@ -20102,7 +20102,7 @@
         <v>0.94602053206755699</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6">
         <v>0.41868386608424402</v>
@@ -20120,7 +20120,7 @@
         <v>b</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7">
         <v>64.409505937268307</v>
@@ -20129,7 +20129,7 @@
         <v>0.94516108684339095</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H7">
         <v>0.19869742797218401</v>
@@ -20143,10 +20143,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8">
         <v>0.189235645687794</v>
@@ -20155,7 +20155,7 @@
         <v>0.89887720183558495</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H8">
         <v>0.189235645687794</v>
@@ -20173,7 +20173,7 @@
         <v>c</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>37.4528882090423</v>
@@ -20182,7 +20182,7 @@
         <v>0.90122687776954202</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H9">
         <v>0.17937962247488601</v>
@@ -20200,7 +20200,7 @@
         <v>c</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10">
         <v>63.558339772601798</v>
@@ -20209,7 +20209,7 @@
         <v>0.90212180467727399</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H10">
         <v>0.38162521880371902</v>
@@ -20223,10 +20223,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>0.17937962247488601</v>
@@ -20235,7 +20235,7 @@
         <v>0.852061091574282</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H11">
         <v>0.37176919559081101</v>
@@ -20253,7 +20253,7 @@
         <v>d</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>33.442669484175099</v>
@@ -20262,7 +20262,7 @@
         <v>0.85268793465062298</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H12">
         <v>0.151388516550234</v>
@@ -20280,7 +20280,7 @@
         <v>d</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>62.285730055351401</v>
@@ -20289,7 +20289,7 @@
         <v>0.85722564773784504</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H13">
         <v>0.35284563102203398</v>
@@ -20303,10 +20303,10 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>0.38162521880371902</v>
@@ -20315,7 +20315,7 @@
         <v>0.81272767413621705</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H14">
         <v>0.13325343383848601</v>
@@ -20333,7 +20333,7 @@
         <v>e</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>29.644552378849699</v>
@@ -20342,7 +20342,7 @@
         <v>0.81163168435494204</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H15">
         <v>0.124185892482614</v>
@@ -20360,7 +20360,7 @@
         <v>e</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>57.854856259757398</v>
@@ -20369,7 +20369,7 @@
         <v>0.81057511866651899</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H16">
         <v>-9.6194786557962403E-2</v>
@@ -20383,10 +20383,10 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17">
         <v>0.37176919559081101</v>
@@ -20395,7 +20395,7 @@
         <v>0.76591156387491499</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17">
         <v>0.105262327913834</v>
@@ -20413,7 +20413,7 @@
         <v>f</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18">
         <v>25.003548168356598</v>
@@ -20422,7 +20422,7 @@
         <v>0.76686168451263903</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H18">
         <v>0.30553671960008399</v>
@@ -20440,7 +20440,7 @@
         <v>f</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19">
         <v>59.319855550123698</v>
@@ -20449,7 +20449,7 @@
         <v>0.76932174790658003</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H19">
         <v>-0.124974374339647</v>
@@ -20463,10 +20463,10 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20">
         <v>0.151388516550234</v>
@@ -20475,7 +20475,7 @@
         <v>0.71910333843218199</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H20">
         <v>0.28661315503130402</v>
@@ -20493,7 +20493,7 @@
         <v>g</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21">
         <v>21.4147729960733</v>
@@ -20502,7 +20502,7 @@
         <v>0.72017961616703197</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H21">
         <v>6.7415198776274096E-2</v>
@@ -20520,7 +20520,7 @@
         <v>g</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22">
         <v>55.098717928500399</v>
@@ -20529,7 +20529,7 @@
         <v>0.71891804519577995</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H22">
         <v>-0.15257123933578101</v>
@@ -20543,10 +20543,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23">
         <v>0.35284563102203398</v>
@@ -20555,7 +20555,7 @@
         <v>0.67602463217321296</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H23">
         <v>-0.162033021620171</v>
@@ -20573,7 +20573,7 @@
         <v>h</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24">
         <v>18.037705202403199</v>
@@ -20582,7 +20582,7 @@
         <v>0.67910759623421002</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H24">
         <v>-0.17149480390456101</v>
@@ -20600,7 +20600,7 @@
         <v>h</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25">
         <v>52.984009587939298</v>
@@ -20609,7 +20609,7 @@
         <v>0.67405342753063202</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H25">
         <v>-0.18056234526043699</v>
@@ -20623,10 +20623,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C26">
         <v>0.13325343383848601</v>
@@ -20635,7 +20635,7 @@
         <v>0.63296169555138504</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H26">
         <v>2.0500528282841601E-2</v>
@@ -20653,7 +20653,7 @@
         <v>i</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C27">
         <v>13.3970952328386</v>
@@ -20662,7 +20662,7 @@
         <v>0.636210240802359</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H27">
         <v>1.14329869269695E-2</v>
@@ -20680,7 +20680,7 @@
         <v>i</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28">
         <v>51.291533281819099</v>
@@ -20691,10 +20691,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C29">
         <v>0.124185892482614</v>
@@ -20709,7 +20709,7 @@
         <v>j</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30">
         <v>9.3864822670430303</v>
@@ -20724,7 +20724,7 @@
         <v>j</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31">
         <v>50.228265497610799</v>
@@ -20735,10 +20735,10 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32">
         <v>-9.6194786557962403E-2</v>
@@ -20753,7 +20753,7 @@
         <v>k</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C33">
         <v>48.744342642675697</v>
@@ -20768,7 +20768,7 @@
         <v>k</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34">
         <v>48.746708088246798</v>
@@ -20779,10 +20779,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C35">
         <v>0.105262327913834</v>
@@ -20797,7 +20797,7 @@
         <v>l</v>
       </c>
       <c r="B36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C36">
         <v>45.789112642517999</v>
@@ -20812,7 +20812,7 @@
         <v>l</v>
       </c>
       <c r="B37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C37">
         <v>49.577767965559097</v>
@@ -20823,10 +20823,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38">
         <v>0.30553671960008399</v>
@@ -20841,7 +20841,7 @@
         <v>m</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C39">
         <v>41.5695519846088</v>
@@ -20856,7 +20856,7 @@
         <v>m</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C40">
         <v>46.200700171888997</v>
@@ -20867,10 +20867,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C41">
         <v>-0.124974374339647</v>
@@ -20885,7 +20885,7 @@
         <v>n</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C42">
         <v>37.558544777884599</v>
@@ -20900,7 +20900,7 @@
         <v>n</v>
       </c>
       <c r="B43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C43">
         <v>46.821629634302099</v>
@@ -20911,10 +20911,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C44">
         <v>0.28661315503130402</v>
@@ -20929,7 +20929,7 @@
         <v>o</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C45">
         <v>33.340166842760901</v>
@@ -20944,7 +20944,7 @@
         <v>o</v>
       </c>
       <c r="B46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C46">
         <v>48.286628924668399</v>
@@ -20955,10 +20955,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C47">
         <v>6.7415198776274096E-2</v>
@@ -20973,7 +20973,7 @@
         <v>p</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C48">
         <v>29.752180152334599</v>
@@ -20988,7 +20988,7 @@
         <v>p</v>
       </c>
       <c r="B49" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C49">
         <v>48.908741109867002</v>
@@ -20999,10 +20999,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C50">
         <v>-0.15257123933578101</v>
@@ -21017,7 +21017,7 @@
         <v>q</v>
       </c>
       <c r="B51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C51">
         <v>25.5322252534969</v>
@@ -21032,7 +21032,7 @@
         <v>q</v>
       </c>
       <c r="B52" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C52">
         <v>66.5845331398924</v>
@@ -21043,10 +21043,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C53">
         <v>-0.162033021620171</v>
@@ -21061,7 +21061,7 @@
         <v>r</v>
       </c>
       <c r="B54" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C54">
         <v>21.7321369435289</v>
@@ -21076,7 +21076,7 @@
         <v>r</v>
       </c>
       <c r="B55" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C55">
         <v>68.890842571712398</v>
@@ -21087,10 +21087,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B56" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C56">
         <v>-0.17149480390456101</v>
@@ -21105,7 +21105,7 @@
         <v>s</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C57">
         <v>17.934019838203501</v>
@@ -21120,7 +21120,7 @@
         <v>s</v>
       </c>
       <c r="B58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C58">
         <v>73.092662387838402</v>
@@ -21131,10 +21131,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C59">
         <v>-0.18056234526043699</v>
@@ -21149,7 +21149,7 @@
         <v>t</v>
       </c>
       <c r="B60" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C60">
         <v>13.503540283537999</v>
@@ -21164,7 +21164,7 @@
         <v>t</v>
       </c>
       <c r="B61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C61">
         <v>76.871855928594996</v>
@@ -21175,10 +21175,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C62">
         <v>2.0500528282841601E-2</v>
@@ -21193,7 +21193,7 @@
         <v>u</v>
       </c>
       <c r="B63" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C63">
         <v>9.4937157995994408</v>
@@ -21208,7 +21208,7 @@
         <v>u</v>
       </c>
       <c r="B64" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C64">
         <v>81.283411918691698</v>
@@ -21219,10 +21219,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C65">
         <v>1.14329869269695E-2</v>
@@ -21237,7 +21237,7 @@
         <v>v</v>
       </c>
       <c r="B66" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C66">
         <v>9.4617822843900898E-3</v>
@@ -21252,7 +21252,7 @@
         <v>v</v>
       </c>
       <c r="B67" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C67">
         <v>79.590935612571499</v>

--- a/Prototypes/Lentil/CEData.xlsx
+++ b/Prototypes/Lentil/CEData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\Lentil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99153353-16CD-465C-90B0-A78A85FDF3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F844CE-765C-4691-AA0E-642ADBCD8B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" activeTab="2" xr2:uid="{A5017088-8F3F-41C2-9D3D-102B2E5948D4}"/>
+    <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{A5017088-8F3F-41C2-9D3D-102B2E5948D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Roberts_etal_1988" sheetId="1" r:id="rId1"/>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>ILL4349</t>
-  </si>
-  <si>
-    <t>Ethiopia</t>
   </si>
   <si>
     <t>Syrian</t>
@@ -240,6 +237,9 @@
   </si>
   <si>
     <t>Lentil.Phenology.StartFloweringTt</t>
+  </si>
+  <si>
+    <t>Ethiopian</t>
   </si>
 </sst>
 </file>
@@ -1234,7 +1234,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1243,25 +1243,25 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" t="s">
-        <v>55</v>
-      </c>
       <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" t="s">
         <v>50</v>
-      </c>
-      <c r="I1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J1" t="s">
-        <v>51</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -1270,7 +1270,7 @@
         <v>2</v>
       </c>
       <c r="M1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -10656,7 +10656,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -10665,34 +10665,34 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" t="s">
         <v>61</v>
       </c>
-      <c r="G1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" t="s">
-        <v>60</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>50</v>
-      </c>
-      <c r="L1" t="s">
-        <v>62</v>
-      </c>
-      <c r="M1" t="s">
-        <v>51</v>
       </c>
       <c r="N1" t="s">
         <v>1</v>
@@ -10701,7 +10701,7 @@
         <v>2</v>
       </c>
       <c r="P1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -12086,10 +12086,10 @@
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp10hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp10hCvEthiopian</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -12143,10 +12143,10 @@
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp10hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp10hCvEthiopian</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -12200,10 +12200,10 @@
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp10hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp10hCvEthiopian</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -12257,10 +12257,10 @@
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp10hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp10hCvEthiopian</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -12314,10 +12314,10 @@
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp13hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp13hCvEthiopian</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -12371,10 +12371,10 @@
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp13hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp13hCvEthiopian</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -12428,10 +12428,10 @@
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp13hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp13hCvEthiopian</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -12485,10 +12485,10 @@
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp13hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp13hCvEthiopian</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -12542,10 +12542,10 @@
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp16hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin5oCFinalPp16hCvEthiopian</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -12599,10 +12599,10 @@
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp16hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat0FinalTmax18oCFinalTmin13oCFinalPp16hCvEthiopian</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
@@ -12656,10 +12656,10 @@
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp16hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin5oCFinalPp16hCvEthiopian</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>4</v>
@@ -12713,10 +12713,10 @@
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp16hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat0FinalTmax28oCFinalTmin13oCFinalPp16hCvEthiopian</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -12770,10 +12770,10 @@
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp10hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp10hCvEthiopian</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -12827,10 +12827,10 @@
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp10hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp10hCvEthiopian</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -12885,10 +12885,10 @@
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp10hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp10hCvEthiopian</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -12943,10 +12943,10 @@
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp10hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp10hCvEthiopian</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
@@ -13001,10 +13001,10 @@
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp13hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp13hCvEthiopian</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -13059,10 +13059,10 @@
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp13hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp13hCvEthiopian</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -13117,10 +13117,10 @@
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp13hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp13hCvEthiopian</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -13175,10 +13175,10 @@
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp13hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp13hCvEthiopian</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -13233,10 +13233,10 @@
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp16hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp16hCvEthiopian</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -13291,10 +13291,10 @@
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp16hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin13oCFinalPp16hCvEthiopian</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -13349,10 +13349,10 @@
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp16hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin5oCFinalPp16hCvEthiopian</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -13407,10 +13407,10 @@
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f t="shared" si="4"/>
-        <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp16hCvEthiopia</v>
+        <v>Summerfield1985InitT1oCDurat30FinalTmax28oCFinalTmin13oCFinalPp16hCvEthiopian</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -14666,7 +14666,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -14675,25 +14675,25 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" t="s">
-        <v>55</v>
-      </c>
       <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" t="s">
         <v>50</v>
-      </c>
-      <c r="I1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J1" t="s">
-        <v>51</v>
       </c>
       <c r="K1" t="s">
         <v>1</v>
@@ -14702,22 +14702,22 @@
         <v>2</v>
       </c>
       <c r="M1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q1" t="s">
         <v>47</v>
       </c>
-      <c r="Q1" t="s">
-        <v>48</v>
-      </c>
       <c r="R1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -14726,10 +14726,10 @@
         <v>Roberts1986Pp10to16hDurat45CvSyrian</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
       </c>
       <c r="D2" s="1">
         <v>10</v>
@@ -14765,7 +14765,7 @@
         <v>1478.5321100917445</v>
       </c>
       <c r="N2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O2">
         <f>F2*MIN(H2,I2)</f>
@@ -14790,10 +14790,10 @@
         <v>Roberts1986Pp10to16hDurat41CvSyrian</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
       </c>
       <c r="D3" s="1">
         <v>10</v>
@@ -14829,7 +14829,7 @@
         <v>1428.623853211009</v>
       </c>
       <c r="N3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O66" si="4">F3*MIN(H3,I3)</f>
@@ -14854,10 +14854,10 @@
         <v>Roberts1986Pp10to16hDurat37CvSyrian</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
       </c>
       <c r="D4" s="1">
         <v>10</v>
@@ -14893,7 +14893,7 @@
         <v>1335.045871559631</v>
       </c>
       <c r="N4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O4">
         <f t="shared" si="4"/>
@@ -14918,10 +14918,10 @@
         <v>Roberts1986Pp10to16hDurat33CvSyrian</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
       </c>
       <c r="D5" s="1">
         <v>10</v>
@@ -14957,7 +14957,7 @@
         <v>1241.4678899082564</v>
       </c>
       <c r="N5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O5">
         <f t="shared" si="4"/>
@@ -14982,10 +14982,10 @@
         <v>Roberts1986Pp10to16hDurat29CvSyrian</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
         <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
       </c>
       <c r="D6" s="1">
         <v>10</v>
@@ -15021,7 +15021,7 @@
         <v>1122.9357798165133</v>
       </c>
       <c r="N6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O6">
         <f t="shared" si="4"/>
@@ -15046,10 +15046,10 @@
         <v>Roberts1986Pp10to16hDurat25CvSyrian</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
         <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
       </c>
       <c r="D7" s="1">
         <v>10</v>
@@ -15085,7 +15085,7 @@
         <v>1066.7889908256873</v>
       </c>
       <c r="N7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O7">
         <f t="shared" si="4"/>
@@ -15110,10 +15110,10 @@
         <v>Roberts1986Pp10to16hDurat21CvSyrian</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
         <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>11</v>
       </c>
       <c r="D8" s="1">
         <v>10</v>
@@ -15149,7 +15149,7 @@
         <v>979.44954128440099</v>
       </c>
       <c r="N8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O8">
         <f t="shared" si="4"/>
@@ -15174,10 +15174,10 @@
         <v>Roberts1986Pp10to16hDurat17CvSyrian</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
         <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
       </c>
       <c r="D9" s="1">
         <v>10</v>
@@ -15213,7 +15213,7 @@
         <v>904.58715596330046</v>
       </c>
       <c r="N9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O9">
         <f t="shared" si="4"/>
@@ -15238,10 +15238,10 @@
         <v>Roberts1986Pp10to16hDurat13CvSyrian</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
         <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>11</v>
       </c>
       <c r="D10" s="1">
         <v>10</v>
@@ -15277,7 +15277,7 @@
         <v>792.29357798164858</v>
       </c>
       <c r="N10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O10">
         <f t="shared" si="4"/>
@@ -15302,10 +15302,10 @@
         <v>Roberts1986Pp10to16hDurat9CvSyrian</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
         <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
       </c>
       <c r="D11" s="1">
         <v>10</v>
@@ -15341,7 +15341,7 @@
         <v>786.05504587155724</v>
       </c>
       <c r="N11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O11">
         <f t="shared" si="4"/>
@@ -15366,10 +15366,10 @@
         <v>Roberts1986Pp10to16hDurat0CvSyrian</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
         <v>10</v>
-      </c>
-      <c r="C12" t="s">
-        <v>11</v>
       </c>
       <c r="D12" s="1">
         <v>10</v>
@@ -15405,7 +15405,7 @@
         <v>748.62385321100896</v>
       </c>
       <c r="N12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O12">
         <f t="shared" si="4"/>
@@ -15430,10 +15430,10 @@
         <v>Roberts1986Pp16to10hDurat45CvSyrian</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
         <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>11</v>
       </c>
       <c r="D13" s="1">
         <v>16</v>
@@ -15469,7 +15469,7 @@
         <v>723.66972477063985</v>
       </c>
       <c r="N13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O13">
         <f t="shared" si="4"/>
@@ -15494,10 +15494,10 @@
         <v>Roberts1986Pp16to10hDurat41CvSyrian</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
         <v>10</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
       </c>
       <c r="D14" s="1">
         <v>16</v>
@@ -15533,7 +15533,7 @@
         <v>748.62385321100896</v>
       </c>
       <c r="N14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O14">
         <f t="shared" si="4"/>
@@ -15558,10 +15558,10 @@
         <v>Roberts1986Pp16to10hDurat37CvSyrian</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
         <v>10</v>
-      </c>
-      <c r="C15" t="s">
-        <v>11</v>
       </c>
       <c r="D15" s="1">
         <v>16</v>
@@ -15597,7 +15597,7 @@
         <v>742.38532110091739</v>
       </c>
       <c r="N15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O15">
         <f t="shared" si="4"/>
@@ -15622,10 +15622,10 @@
         <v>Roberts1986Pp16to10hDurat33CvSyrian</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
         <v>10</v>
-      </c>
-      <c r="C16" t="s">
-        <v>11</v>
       </c>
       <c r="D16" s="1">
         <v>16</v>
@@ -15661,7 +15661,7 @@
         <v>748.62385321100896</v>
       </c>
       <c r="N16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O16">
         <f t="shared" si="4"/>
@@ -15686,10 +15686,10 @@
         <v>Roberts1986Pp16to10hDurat29CvSyrian</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
         <v>10</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
       </c>
       <c r="D17" s="1">
         <v>16</v>
@@ -15725,7 +15725,7 @@
         <v>765</v>
       </c>
       <c r="N17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O17">
         <f t="shared" si="4"/>
@@ -15750,10 +15750,10 @@
         <v>Roberts1986Pp16to10hDurat25CvSyrian</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
         <v>10</v>
-      </c>
-      <c r="C18" t="s">
-        <v>11</v>
       </c>
       <c r="D18" s="1">
         <v>16</v>
@@ -15789,7 +15789,7 @@
         <v>754.86238532110019</v>
       </c>
       <c r="N18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O18">
         <f t="shared" si="4"/>
@@ -15814,10 +15814,10 @@
         <v>Roberts1986Pp16to10hDurat21CvSyrian</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
         <v>10</v>
-      </c>
-      <c r="C19" t="s">
-        <v>11</v>
       </c>
       <c r="D19" s="1">
         <v>16</v>
@@ -15853,7 +15853,7 @@
         <v>2046.2385321100915</v>
       </c>
       <c r="N19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O19">
         <f t="shared" si="4"/>
@@ -15878,10 +15878,10 @@
         <v>Roberts1986Pp16to10hDurat17CvSyrian</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
         <v>10</v>
-      </c>
-      <c r="C20" t="s">
-        <v>11</v>
       </c>
       <c r="D20" s="1">
         <v>16</v>
@@ -15917,7 +15917,7 @@
         <v>2832.2935779816517</v>
       </c>
       <c r="N20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O20">
         <f t="shared" si="4"/>
@@ -15942,10 +15942,10 @@
         <v>Roberts1986Pp16to10hDurat13CvSyrian</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
         <v>10</v>
-      </c>
-      <c r="C21" t="s">
-        <v>11</v>
       </c>
       <c r="D21" s="1">
         <v>16</v>
@@ -15981,7 +15981,7 @@
         <v>2944.5871559633006</v>
       </c>
       <c r="N21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O21">
         <f t="shared" si="4"/>
@@ -16006,10 +16006,10 @@
         <v>Roberts1986Pp16to10hDurat9CvSyrian</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
         <v>10</v>
-      </c>
-      <c r="C22" t="s">
-        <v>11</v>
       </c>
       <c r="D22" s="1">
         <v>16</v>
@@ -16045,7 +16045,7 @@
         <v>2189.7247706422004</v>
       </c>
       <c r="N22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O22">
         <f t="shared" si="4"/>
@@ -16070,10 +16070,10 @@
         <v>Roberts1986Pp16to10hDurat0CvSyrian</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
         <v>10</v>
-      </c>
-      <c r="C23" t="s">
-        <v>11</v>
       </c>
       <c r="D23" s="1">
         <v>16</v>
@@ -16109,7 +16109,7 @@
         <v>2713.7614678899085</v>
       </c>
       <c r="N23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O23">
         <f t="shared" si="4"/>
@@ -16173,7 +16173,7 @@
         <v>1448.4333101074726</v>
       </c>
       <c r="N24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O24">
         <f t="shared" si="4"/>
@@ -16237,7 +16237,7 @@
         <v>1293.0549397183331</v>
       </c>
       <c r="N25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O25">
         <f t="shared" si="4"/>
@@ -16301,7 +16301,7 @@
         <v>1289.8872490023416</v>
       </c>
       <c r="N26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O26">
         <f t="shared" si="4"/>
@@ -16365,7 +16365,7 @@
         <v>1226.8834061780783</v>
       </c>
       <c r="N27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O27">
         <f t="shared" si="4"/>
@@ -16429,7 +16429,7 @@
         <v>1246.8407550516242</v>
       </c>
       <c r="N28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O28">
         <f t="shared" si="4"/>
@@ -16493,7 +16493,7 @@
         <v>1234.4481746584738</v>
       </c>
       <c r="N29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O29">
         <f t="shared" si="4"/>
@@ -16557,7 +16557,7 @@
         <v>1175.805515086251</v>
       </c>
       <c r="N30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O30">
         <f t="shared" si="4"/>
@@ -16621,7 +16621,7 @@
         <v>1186.4751588860031</v>
       </c>
       <c r="N31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O31">
         <f t="shared" si="4"/>
@@ -16685,7 +16685,7 @@
         <v>1151.0831696965845</v>
       </c>
       <c r="N32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O32">
         <f t="shared" si="4"/>
@@ -16749,7 +16749,7 @@
         <v>1170.9148877768614</v>
       </c>
       <c r="N33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O33">
         <f t="shared" si="4"/>
@@ -16813,7 +16813,7 @@
         <v>1144.7477882646058</v>
       </c>
       <c r="N34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O34">
         <f t="shared" si="4"/>
@@ -16877,7 +16877,7 @@
         <v>1187.7045459344179</v>
       </c>
       <c r="N35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O35">
         <f t="shared" si="4"/>
@@ -16941,7 +16941,7 @@
         <v>1161.4746310255266</v>
       </c>
       <c r="N36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O36">
         <f t="shared" si="4"/>
@@ -17005,7 +17005,7 @@
         <v>1453.5034099786728</v>
       </c>
       <c r="N37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O37">
         <f t="shared" si="4"/>
@@ -17069,7 +17069,7 @@
         <v>1676.4711471463841</v>
       </c>
       <c r="N38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O38">
         <f t="shared" si="4"/>
@@ -17133,7 +17133,7 @@
         <v>1354.9819471717219</v>
       </c>
       <c r="N39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O39">
         <f t="shared" si="4"/>
@@ -17197,7 +17197,7 @@
         <v>1997.5565338569704</v>
       </c>
       <c r="N40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O40">
         <f t="shared" si="4"/>
@@ -17261,7 +17261,7 @@
         <v>1929.8146154008555</v>
       </c>
       <c r="N41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O41">
         <f t="shared" si="4"/>
@@ -17325,7 +17325,7 @@
         <v>2143.4946474947692</v>
       </c>
       <c r="N42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O42">
         <f t="shared" si="4"/>
@@ -17389,7 +17389,7 @@
         <v>2463.3865416692888</v>
       </c>
       <c r="N43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O43">
         <f t="shared" si="4"/>
@@ -17453,7 +17453,7 @@
         <v>2229.4709782310288</v>
       </c>
       <c r="N44" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O44">
         <f t="shared" si="4"/>
@@ -17517,7 +17517,7 @@
         <v>1861.8573298705689</v>
       </c>
       <c r="N45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O45">
         <f t="shared" si="4"/>
@@ -17581,7 +17581,7 @@
         <v>1120.5163142213498</v>
       </c>
       <c r="N46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O46">
         <f t="shared" si="4"/>
@@ -17645,7 +17645,7 @@
         <v>1087.7170990480333</v>
       </c>
       <c r="N47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O47">
         <f t="shared" si="4"/>
@@ -17709,7 +17709,7 @@
         <v>1140.7764697333041</v>
       </c>
       <c r="N48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O48">
         <f t="shared" si="4"/>
@@ -17773,7 +17773,7 @@
         <v>1095.0984666811999</v>
       </c>
       <c r="N49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O49">
         <f t="shared" si="4"/>
@@ -17837,7 +17837,7 @@
         <v>1058.0680909817593</v>
       </c>
       <c r="N50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O50">
         <f t="shared" si="4"/>
@@ -17901,7 +17901,7 @@
         <v>986.6942809388845</v>
       </c>
       <c r="N51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O51">
         <f t="shared" si="4"/>
@@ -17965,7 +17965,7 @@
         <v>962.48092435142655</v>
       </c>
       <c r="N52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O52">
         <f t="shared" si="4"/>
@@ -18029,7 +18029,7 @@
         <v>912.32468570598076</v>
       </c>
       <c r="N53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O53">
         <f t="shared" si="4"/>
@@ -18093,7 +18093,7 @@
         <v>871.00138071361073</v>
       </c>
       <c r="N54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O54">
         <f t="shared" si="4"/>
@@ -18157,7 +18157,7 @@
         <v>838.38747184070905</v>
       </c>
       <c r="N55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O55">
         <f t="shared" si="4"/>
@@ -18221,7 +18221,7 @@
         <v>839.86992224402172</v>
       </c>
       <c r="N56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O56">
         <f t="shared" si="4"/>
@@ -18285,7 +18285,7 @@
         <v>858.46232105224874</v>
       </c>
       <c r="N57" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O57">
         <f t="shared" si="4"/>
@@ -18349,7 +18349,7 @@
         <v>851.54421917011757</v>
       </c>
       <c r="N58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O58">
         <f t="shared" si="4"/>
@@ -18413,7 +18413,7 @@
         <v>861.6742969260938</v>
       </c>
       <c r="N59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O59">
         <f t="shared" si="4"/>
@@ -18477,7 +18477,7 @@
         <v>824.58215245985025</v>
       </c>
       <c r="N60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O60">
         <f t="shared" si="4"/>
@@ -18541,7 +18541,7 @@
         <v>890.52031102390652</v>
       </c>
       <c r="N61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O61">
         <f t="shared" si="4"/>
@@ -18605,7 +18605,7 @@
         <v>952.28907782864565</v>
       </c>
       <c r="N62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O62">
         <f t="shared" si="4"/>
@@ -18669,7 +18669,7 @@
         <v>966.58854734394129</v>
       </c>
       <c r="N63" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O63">
         <f t="shared" si="4"/>
@@ -18733,7 +18733,7 @@
         <v>1152.7904948768257</v>
       </c>
       <c r="N64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O64">
         <f t="shared" si="4"/>
@@ -18797,7 +18797,7 @@
         <v>1132.931836349102</v>
       </c>
       <c r="N65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O65">
         <f t="shared" si="4"/>
@@ -18861,7 +18861,7 @@
         <v>1146.9842307971803</v>
       </c>
       <c r="N66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O66">
         <f t="shared" si="4"/>
@@ -18925,7 +18925,7 @@
         <v>1161.777850446915</v>
       </c>
       <c r="N67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O67">
         <f t="shared" ref="O67" si="12">F67*MIN(H67,I67)</f>
@@ -18986,7 +18986,7 @@
         <v>1630.1396322520613</v>
       </c>
       <c r="N68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
@@ -19031,7 +19031,7 @@
         <v>1390.0948717140002</v>
       </c>
       <c r="N69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
@@ -19076,7 +19076,7 @@
         <v>1365.8459653383368</v>
       </c>
       <c r="N70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
@@ -19121,7 +19121,7 @@
         <v>1332.9574661347037</v>
       </c>
       <c r="N71" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
@@ -19166,7 +19166,7 @@
         <v>1235.3245533250265</v>
       </c>
       <c r="N72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
@@ -19211,7 +19211,7 @@
         <v>1258.5570387775358</v>
       </c>
       <c r="N73" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
@@ -19256,7 +19256,7 @@
         <v>1165.2237175342582</v>
       </c>
       <c r="N74" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
@@ -19301,7 +19301,7 @@
         <v>1115.0721965527555</v>
       </c>
       <c r="N75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
@@ -19346,7 +19346,7 @@
         <v>1073.5764322772916</v>
       </c>
       <c r="N76" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
@@ -19391,7 +19391,7 @@
         <v>1044.9794427010213</v>
       </c>
       <c r="N77" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
@@ -19436,7 +19436,7 @@
         <v>1082.1769195590789</v>
       </c>
       <c r="N78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
@@ -19481,7 +19481,7 @@
         <v>999.3075158090594</v>
       </c>
       <c r="N79" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
@@ -19526,7 +19526,7 @@
         <v>1024.126448835412</v>
       </c>
       <c r="N80" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
@@ -19571,7 +19571,7 @@
         <v>955.9555438159357</v>
       </c>
       <c r="N81" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
@@ -19616,7 +19616,7 @@
         <v>976.54017788150657</v>
       </c>
       <c r="N82" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
@@ -19661,7 +19661,7 @@
         <v>1015.8631621276385</v>
       </c>
       <c r="N83" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
@@ -19706,7 +19706,7 @@
         <v>1036.4740526390474</v>
       </c>
       <c r="N84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
@@ -19751,7 +19751,7 @@
         <v>1435.6766357056113</v>
       </c>
       <c r="N85" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
@@ -19796,7 +19796,7 @@
         <v>1493.6767050920153</v>
       </c>
       <c r="N86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
@@ -19841,7 +19841,7 @@
         <v>1593.7571050100125</v>
       </c>
       <c r="N87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
@@ -19886,7 +19886,7 @@
         <v>1684.4552016148089</v>
       </c>
       <c r="N88" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
@@ -19931,7 +19931,7 @@
         <v>1789.1917445949557</v>
       </c>
       <c r="N89" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
@@ -19976,7 +19976,7 @@
         <v>1766.9187705990873</v>
       </c>
       <c r="N90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
@@ -19999,24 +19999,24 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s">
         <v>41</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>42</v>
-      </c>
-      <c r="D1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2">
         <v>0.41868386608424402</v>
@@ -20031,7 +20031,7 @@
         <v>A</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C3">
         <v>45.0506993834071</v>
@@ -20046,7 +20046,7 @@
         <v>A</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4">
         <v>75.787299134246894</v>
@@ -20055,18 +20055,18 @@
         <v>0.98967877249144398</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5">
         <v>0.19869742797218401</v>
@@ -20075,16 +20075,16 @@
         <v>0.94382066768643602</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
         <v>36</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>37</v>
-      </c>
-      <c r="J5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -20093,7 +20093,7 @@
         <v>b</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6">
         <v>41.462318452052401</v>
@@ -20102,7 +20102,7 @@
         <v>0.94602053206755699</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6">
         <v>0.41868386608424402</v>
@@ -20120,7 +20120,7 @@
         <v>b</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>64.409505937268307</v>
@@ -20129,7 +20129,7 @@
         <v>0.94516108684339095</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H7">
         <v>0.19869742797218401</v>
@@ -20143,10 +20143,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>0.189235645687794</v>
@@ -20155,7 +20155,7 @@
         <v>0.89887720183558495</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H8">
         <v>0.189235645687794</v>
@@ -20173,7 +20173,7 @@
         <v>c</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>37.4528882090423</v>
@@ -20182,7 +20182,7 @@
         <v>0.90122687776954202</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H9">
         <v>0.17937962247488601</v>
@@ -20200,7 +20200,7 @@
         <v>c</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>63.558339772601798</v>
@@ -20209,7 +20209,7 @@
         <v>0.90212180467727399</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H10">
         <v>0.38162521880371902</v>
@@ -20223,10 +20223,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>0.17937962247488601</v>
@@ -20235,7 +20235,7 @@
         <v>0.852061091574282</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H11">
         <v>0.37176919559081101</v>
@@ -20253,7 +20253,7 @@
         <v>d</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>33.442669484175099</v>
@@ -20262,7 +20262,7 @@
         <v>0.85268793465062298</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H12">
         <v>0.151388516550234</v>
@@ -20280,7 +20280,7 @@
         <v>d</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>62.285730055351401</v>
@@ -20289,7 +20289,7 @@
         <v>0.85722564773784504</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H13">
         <v>0.35284563102203398</v>
@@ -20303,10 +20303,10 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>0.38162521880371902</v>
@@ -20315,7 +20315,7 @@
         <v>0.81272767413621705</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H14">
         <v>0.13325343383848601</v>
@@ -20333,7 +20333,7 @@
         <v>e</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15">
         <v>29.644552378849699</v>
@@ -20342,7 +20342,7 @@
         <v>0.81163168435494204</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H15">
         <v>0.124185892482614</v>
@@ -20360,7 +20360,7 @@
         <v>e</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C16">
         <v>57.854856259757398</v>
@@ -20369,7 +20369,7 @@
         <v>0.81057511866651899</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H16">
         <v>-9.6194786557962403E-2</v>
@@ -20383,10 +20383,10 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C17">
         <v>0.37176919559081101</v>
@@ -20395,7 +20395,7 @@
         <v>0.76591156387491499</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H17">
         <v>0.105262327913834</v>
@@ -20413,7 +20413,7 @@
         <v>f</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18">
         <v>25.003548168356598</v>
@@ -20422,7 +20422,7 @@
         <v>0.76686168451263903</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H18">
         <v>0.30553671960008399</v>
@@ -20440,7 +20440,7 @@
         <v>f</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19">
         <v>59.319855550123698</v>
@@ -20449,7 +20449,7 @@
         <v>0.76932174790658003</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H19">
         <v>-0.124974374339647</v>
@@ -20463,10 +20463,10 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20">
         <v>0.151388516550234</v>
@@ -20475,7 +20475,7 @@
         <v>0.71910333843218199</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H20">
         <v>0.28661315503130402</v>
@@ -20493,7 +20493,7 @@
         <v>g</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>21.4147729960733</v>
@@ -20502,7 +20502,7 @@
         <v>0.72017961616703197</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H21">
         <v>6.7415198776274096E-2</v>
@@ -20520,7 +20520,7 @@
         <v>g</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22">
         <v>55.098717928500399</v>
@@ -20529,7 +20529,7 @@
         <v>0.71891804519577995</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H22">
         <v>-0.15257123933578101</v>
@@ -20543,10 +20543,10 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23">
         <v>0.35284563102203398</v>
@@ -20555,7 +20555,7 @@
         <v>0.67602463217321296</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H23">
         <v>-0.162033021620171</v>
@@ -20573,7 +20573,7 @@
         <v>h</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24">
         <v>18.037705202403199</v>
@@ -20582,7 +20582,7 @@
         <v>0.67910759623421002</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H24">
         <v>-0.17149480390456101</v>
@@ -20600,7 +20600,7 @@
         <v>h</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C25">
         <v>52.984009587939298</v>
@@ -20609,7 +20609,7 @@
         <v>0.67405342753063202</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H25">
         <v>-0.18056234526043699</v>
@@ -20623,10 +20623,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C26">
         <v>0.13325343383848601</v>
@@ -20635,7 +20635,7 @@
         <v>0.63296169555138504</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H26">
         <v>2.0500528282841601E-2</v>
@@ -20653,7 +20653,7 @@
         <v>i</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C27">
         <v>13.3970952328386</v>
@@ -20662,7 +20662,7 @@
         <v>0.636210240802359</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H27">
         <v>1.14329869269695E-2</v>
@@ -20680,7 +20680,7 @@
         <v>i</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28">
         <v>51.291533281819099</v>
@@ -20691,10 +20691,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29">
         <v>0.124185892482614</v>
@@ -20709,7 +20709,7 @@
         <v>j</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30">
         <v>9.3864822670430303</v>
@@ -20724,7 +20724,7 @@
         <v>j</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31">
         <v>50.228265497610799</v>
@@ -20735,10 +20735,10 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C32">
         <v>-9.6194786557962403E-2</v>
@@ -20753,7 +20753,7 @@
         <v>k</v>
       </c>
       <c r="B33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C33">
         <v>48.744342642675697</v>
@@ -20768,7 +20768,7 @@
         <v>k</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C34">
         <v>48.746708088246798</v>
@@ -20779,10 +20779,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35">
         <v>0.105262327913834</v>
@@ -20797,7 +20797,7 @@
         <v>l</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36">
         <v>45.789112642517999</v>
@@ -20812,7 +20812,7 @@
         <v>l</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C37">
         <v>49.577767965559097</v>
@@ -20823,10 +20823,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C38">
         <v>0.30553671960008399</v>
@@ -20841,7 +20841,7 @@
         <v>m</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C39">
         <v>41.5695519846088</v>
@@ -20856,7 +20856,7 @@
         <v>m</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C40">
         <v>46.200700171888997</v>
@@ -20867,10 +20867,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C41">
         <v>-0.124974374339647</v>
@@ -20885,7 +20885,7 @@
         <v>n</v>
       </c>
       <c r="B42" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C42">
         <v>37.558544777884599</v>
@@ -20900,7 +20900,7 @@
         <v>n</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C43">
         <v>46.821629634302099</v>
@@ -20911,10 +20911,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C44">
         <v>0.28661315503130402</v>
@@ -20929,7 +20929,7 @@
         <v>o</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C45">
         <v>33.340166842760901</v>
@@ -20944,7 +20944,7 @@
         <v>o</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C46">
         <v>48.286628924668399</v>
@@ -20955,10 +20955,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C47">
         <v>6.7415198776274096E-2</v>
@@ -20973,7 +20973,7 @@
         <v>p</v>
       </c>
       <c r="B48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C48">
         <v>29.752180152334599</v>
@@ -20988,7 +20988,7 @@
         <v>p</v>
       </c>
       <c r="B49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C49">
         <v>48.908741109867002</v>
@@ -20999,10 +20999,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B50" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C50">
         <v>-0.15257123933578101</v>
@@ -21017,7 +21017,7 @@
         <v>q</v>
       </c>
       <c r="B51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C51">
         <v>25.5322252534969</v>
@@ -21032,7 +21032,7 @@
         <v>q</v>
       </c>
       <c r="B52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C52">
         <v>66.5845331398924</v>
@@ -21043,10 +21043,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C53">
         <v>-0.162033021620171</v>
@@ -21061,7 +21061,7 @@
         <v>r</v>
       </c>
       <c r="B54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C54">
         <v>21.7321369435289</v>
@@ -21076,7 +21076,7 @@
         <v>r</v>
       </c>
       <c r="B55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C55">
         <v>68.890842571712398</v>
@@ -21087,10 +21087,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C56">
         <v>-0.17149480390456101</v>
@@ -21105,7 +21105,7 @@
         <v>s</v>
       </c>
       <c r="B57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C57">
         <v>17.934019838203501</v>
@@ -21120,7 +21120,7 @@
         <v>s</v>
       </c>
       <c r="B58" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C58">
         <v>73.092662387838402</v>
@@ -21131,10 +21131,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C59">
         <v>-0.18056234526043699</v>
@@ -21149,7 +21149,7 @@
         <v>t</v>
       </c>
       <c r="B60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C60">
         <v>13.503540283537999</v>
@@ -21164,7 +21164,7 @@
         <v>t</v>
       </c>
       <c r="B61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C61">
         <v>76.871855928594996</v>
@@ -21175,10 +21175,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B62" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C62">
         <v>2.0500528282841601E-2</v>
@@ -21193,7 +21193,7 @@
         <v>u</v>
       </c>
       <c r="B63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C63">
         <v>9.4937157995994408</v>
@@ -21208,7 +21208,7 @@
         <v>u</v>
       </c>
       <c r="B64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C64">
         <v>81.283411918691698</v>
@@ -21219,10 +21219,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C65">
         <v>1.14329869269695E-2</v>
@@ -21237,7 +21237,7 @@
         <v>v</v>
       </c>
       <c r="B66" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C66">
         <v>9.4617822843900898E-3</v>
@@ -21252,7 +21252,7 @@
         <v>v</v>
       </c>
       <c r="B67" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C67">
         <v>79.590935612571499</v>

--- a/Prototypes/Lentil/CEData.xlsx
+++ b/Prototypes/Lentil/CEData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\Lentil\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832B1E0E-EC88-471C-80A4-9C1E64CE3919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90801981-4F71-4461-A9EF-D7E317546F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{A5017088-8F3F-41C2-9D3D-102B2E5948D4}"/>
   </bookViews>
@@ -15430,7 +15430,7 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
-        <f t="shared" ref="A66:A97" si="15">"Summerfield1985InitT1oCDurat"&amp;L66&amp;"FinalTmax"&amp;K66&amp;"oCFinalTmin"&amp;J66&amp;"oCFinalPp"&amp;E66&amp;"hCv"&amp;B66</f>
+        <f t="shared" ref="A66:A73" si="15">"Summerfield1985InitT1oCDurat"&amp;L66&amp;"FinalTmax"&amp;K66&amp;"oCFinalTmin"&amp;J66&amp;"oCFinalPp"&amp;E66&amp;"hCv"&amp;B66</f>
         <v>Summerfield1985InitT1oCDurat30FinalTmax18oCFinalTmin5oCFinalPp13hCvLaird</v>
       </c>
       <c r="B66" t="s">
@@ -20240,7 +20240,7 @@
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
-        <f t="shared" ref="A66:A97" si="9">"Roberts1986Pp"&amp;D66&amp;"to"&amp;E66&amp;"hDurat"&amp;H66&amp;"Cv"&amp;B66</f>
+        <f t="shared" ref="A66:A90" si="9">"Roberts1986Pp"&amp;D66&amp;"to"&amp;E66&amp;"hDurat"&amp;H66&amp;"Cv"&amp;B66</f>
         <v>Roberts1986Pp16to10hDurat9CvPrecoz</v>
       </c>
       <c r="B66" t="s">
@@ -21486,13 +21486,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{541E6961-4D78-4BEA-A16F-03B8897F550D}">
-  <dimension ref="A1:E354"/>
+  <dimension ref="A1:D354"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -21502,11 +21502,11 @@
       <c r="C1" t="s">
         <v>39</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>56</v>
       </c>
@@ -21517,7 +21517,7 @@
         <v>59.749026395499797</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>57</v>
       </c>
@@ -21528,7 +21528,7 @@
         <v>62.237126784941601</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>58</v>
       </c>
@@ -21539,7 +21539,7 @@
         <v>74.811769796624802</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -21550,7 +21550,7 @@
         <v>97.979229770662002</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -21561,7 +21561,7 @@
         <v>59.2427520553872</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -21572,7 +21572,7 @@
         <v>60.212029424491497</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>62</v>
       </c>
@@ -21583,7 +21583,7 @@
         <v>69.2427520553872</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>63</v>
       </c>
@@ -21594,7 +21594,7 @@
         <v>94.435309389874504</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>64</v>
       </c>
@@ -21605,7 +21605,7 @@
         <v>59.247079186499299</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>65</v>
       </c>
@@ -21616,7 +21616,7 @@
         <v>57.680657723929002</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>66</v>
       </c>
@@ -21627,7 +21627,7 @@
         <v>71.267849415837304</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>67</v>
       </c>
@@ -21638,7 +21638,7 @@
         <v>87.343141497187304</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -21649,7 +21649,7 @@
         <v>59.592111639982605</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>69</v>
       </c>
@@ -21660,7 +21660,7 @@
         <v>56.5111942881869</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>70</v>
       </c>
@@ -25311,7 +25311,7 @@
       <c r="B332" t="s">
         <v>55</v>
       </c>
-      <c r="D332">
+      <c r="C332">
         <v>75.787299134246894</v>
       </c>
     </row>
@@ -25322,7 +25322,7 @@
       <c r="B333" t="s">
         <v>55</v>
       </c>
-      <c r="D333">
+      <c r="C333">
         <v>64.409505937268307</v>
       </c>
     </row>
@@ -25333,7 +25333,7 @@
       <c r="B334" t="s">
         <v>55</v>
       </c>
-      <c r="D334">
+      <c r="C334">
         <v>63.558339772601798</v>
       </c>
     </row>
@@ -25344,7 +25344,7 @@
       <c r="B335" t="s">
         <v>55</v>
       </c>
-      <c r="D335">
+      <c r="C335">
         <v>62.285730055351401</v>
       </c>
     </row>
@@ -25355,205 +25355,205 @@
       <c r="B336" t="s">
         <v>55</v>
       </c>
-      <c r="D336">
+      <c r="C336">
         <v>57.854856259757398</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>391</v>
       </c>
       <c r="B337" t="s">
         <v>55</v>
       </c>
-      <c r="D337">
+      <c r="C337">
         <v>59.319855550123698</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>392</v>
       </c>
       <c r="B338" t="s">
         <v>55</v>
       </c>
-      <c r="D338">
+      <c r="C338">
         <v>55.098717928500399</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>393</v>
       </c>
       <c r="B339" t="s">
         <v>55</v>
       </c>
-      <c r="D339">
+      <c r="C339">
         <v>52.984009587939298</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>394</v>
       </c>
       <c r="B340" t="s">
         <v>55</v>
       </c>
-      <c r="D340">
+      <c r="C340">
         <v>51.291533281819099</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>395</v>
       </c>
       <c r="B341" t="s">
         <v>55</v>
       </c>
-      <c r="D341">
+      <c r="C341">
         <v>50.228265497610799</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>396</v>
       </c>
       <c r="B342" t="s">
         <v>55</v>
       </c>
-      <c r="D342">
+      <c r="C342">
         <v>48.746708088246798</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>397</v>
       </c>
       <c r="B343" t="s">
         <v>55</v>
       </c>
-      <c r="D343">
+      <c r="C343">
         <v>48.746708088246798</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>398</v>
       </c>
       <c r="B344" t="s">
         <v>55</v>
       </c>
-      <c r="D344">
+      <c r="C344">
         <v>49.577767965559097</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>399</v>
       </c>
       <c r="B345" t="s">
         <v>55</v>
       </c>
-      <c r="D345">
+      <c r="C345">
         <v>46.200700171888997</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>400</v>
       </c>
       <c r="B346" t="s">
         <v>55</v>
       </c>
-      <c r="D346">
+      <c r="C346">
         <v>46.821629634302099</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>401</v>
       </c>
       <c r="B347" t="s">
         <v>55</v>
       </c>
-      <c r="D347">
+      <c r="C347">
         <v>48.286628924668399</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>402</v>
       </c>
       <c r="B348" t="s">
         <v>55</v>
       </c>
-      <c r="D348">
+      <c r="C348">
         <v>48.908741109867002</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>403</v>
       </c>
       <c r="B349" t="s">
         <v>55</v>
       </c>
-      <c r="D349">
+      <c r="C349">
         <v>66.5845331398924</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>404</v>
       </c>
       <c r="B350" t="s">
         <v>55</v>
       </c>
-      <c r="D350">
+      <c r="C350">
         <v>68.890842571712398</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>405</v>
       </c>
       <c r="B351" t="s">
         <v>55</v>
       </c>
-      <c r="D351">
+      <c r="C351">
         <v>73.092662387838402</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>406</v>
       </c>
       <c r="B352" t="s">
         <v>55</v>
       </c>
-      <c r="D352">
+      <c r="C352">
         <v>76.871855928594996</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>407</v>
       </c>
       <c r="B353" t="s">
         <v>55</v>
       </c>
-      <c r="D353">
+      <c r="C353">
         <v>81.283411918691698</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>408</v>
       </c>
       <c r="B354" t="s">
         <v>55</v>
       </c>
-      <c r="D354">
+      <c r="C354">
         <v>79.590935612571499</v>
       </c>
     </row>
